--- a/design/tables/WaveGroup.xlsx
+++ b/design/tables/WaveGroup.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="R3163c37fdfc34f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="Rb4145054d1d3495f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6390,6 +6390,1317 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
+    <x:row r="360">
+      <x:c r="A360" t="n">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B360" t="n">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="C360" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D360" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E360" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B361" t="n">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="C361" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D361" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E361" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B362" t="n">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="C362" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D362" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E362" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363">
+      <x:c r="A363" t="n">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B363" t="n">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="C363" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D363" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E363" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364">
+      <x:c r="A364" t="n">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B364" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="C364" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D364" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E364" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365">
+      <x:c r="A365" t="n">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B365" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="C365" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D365" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E365" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366">
+      <x:c r="A366" t="n">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B366" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="C366" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D366" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E366" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367">
+      <x:c r="A367" t="n">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B367" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="C367" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D367" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E367" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368">
+      <x:c r="A368" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B368" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="C368" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D368" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E368" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369">
+      <x:c r="A369" t="n">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B369" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="C369" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D369" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E369" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370">
+      <x:c r="A370" t="n">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B370" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="C370" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D370" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E370" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371">
+      <x:c r="A371" t="n">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B371" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="C371" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D371" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E371" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372">
+      <x:c r="A372" t="n">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B372" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C372" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D372" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E372" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373">
+      <x:c r="A373" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B373" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C373" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D373" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E373" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374">
+      <x:c r="A374" t="n">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B374" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C374" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D374" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E374" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375">
+      <x:c r="A375" t="n">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B375" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C375" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D375" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E375" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376">
+      <x:c r="A376" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B376" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C376" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D376" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E376" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377">
+      <x:c r="A377" t="n">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B377" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C377" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D377" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E377" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378">
+      <x:c r="A378" t="n">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B378" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C378" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D378" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E378" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379">
+      <x:c r="A379" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B379" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C379" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D379" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E379" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380">
+      <x:c r="A380" t="n">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B380" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C380" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D380" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E380" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381">
+      <x:c r="A381" t="n">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B381" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C381" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D381" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E381" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382">
+      <x:c r="A382" t="n">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="B382" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C382" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D382" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E382" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383">
+      <x:c r="A383" t="n">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B383" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C383" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D383" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E383" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384">
+      <x:c r="A384" t="n">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B384" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C384" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D384" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E384" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385">
+      <x:c r="A385" t="n">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="B385" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C385" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D385" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E385" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386">
+      <x:c r="A386" t="n">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B386" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C386" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D386" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E386" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387" t="n">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B387" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C387" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D387" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E387" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388" t="n">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B388" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C388" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D388" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E388" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389" t="n">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B389" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C389" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E389" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390" t="n">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B390" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C390" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E390" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391" t="n">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="B391" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C391" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E391" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B392" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C392" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E392" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B393" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C393" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D393" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E393" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394">
+      <x:c r="A394" t="n">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B394" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C394" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D394" t="str">
+        <x:v>postmaster</x:v>
+      </x:c>
+      <x:c r="E394" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395" t="n">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B395" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C395" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D395" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E395" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396">
+      <x:c r="A396" t="n">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B396" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C396" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D396" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E396" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397">
+      <x:c r="A397" t="n">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B397" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C397" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D397" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E397" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398">
+      <x:c r="A398" t="n">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B398" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C398" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D398" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E398" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399">
+      <x:c r="A399" t="n">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B399" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C399" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D399" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E399" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400">
+      <x:c r="A400" t="n">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B400" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C400" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D400" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E400" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401">
+      <x:c r="A401" t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B401" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C401" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D401" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E401" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402">
+      <x:c r="A402" t="n">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B402" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C402" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D402" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E402" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403">
+      <x:c r="A403" t="n">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B403" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C403" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D403" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E403" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404">
+      <x:c r="A404" t="n">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B404" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C404" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D404" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E404" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405">
+      <x:c r="A405" t="n">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B405" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C405" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D405" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E405" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406">
+      <x:c r="A406" t="n">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="B406" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C406" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D406" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E406" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407">
+      <x:c r="A407" t="n">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B407" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C407" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D407" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E407" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408">
+      <x:c r="A408" t="n">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B408" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C408" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D408" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E408" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409">
+      <x:c r="A409" t="n">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B409" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C409" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D409" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E409" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410">
+      <x:c r="A410" t="n">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="B410" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="C410" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D410" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E410" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411">
+      <x:c r="A411" t="n">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B411" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="C411" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D411" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E411" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412">
+      <x:c r="A412" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B412" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="C412" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D412" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E412" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413">
+      <x:c r="A413" t="n">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B413" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="C413" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D413" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E413" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414">
+      <x:c r="A414" t="n">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B414" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="C414" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D414" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E414" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415">
+      <x:c r="A415" t="n">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B415" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="C415" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D415" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E415" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416">
+      <x:c r="A416" t="n">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B416" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C416" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D416" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E416" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417">
+      <x:c r="A417" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B417" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C417" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D417" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E417" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418">
+      <x:c r="A418" t="n">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B418" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C418" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D418" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E418" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419">
+      <x:c r="A419" t="n">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B419" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C419" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D419" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E419" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420">
+      <x:c r="A420" t="n">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B420" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C420" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D420" t="str">
+        <x:v>clock</x:v>
+      </x:c>
+      <x:c r="E420" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421">
+      <x:c r="A421" t="n">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B421" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C421" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D421" t="str">
+        <x:v>postmaster</x:v>
+      </x:c>
+      <x:c r="E421" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422">
+      <x:c r="A422" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B422" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C422" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D422" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E422" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423">
+      <x:c r="A423" t="n">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B423" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C423" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D423" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E423" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424">
+      <x:c r="A424" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B424" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C424" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D424" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E424" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425">
+      <x:c r="A425" t="n">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="B425" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="C425" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D425" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E425" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426">
+      <x:c r="A426"/>
+      <x:c r="B426"/>
+      <x:c r="C426"/>
+      <x:c r="D426"/>
+      <x:c r="E426"/>
+    </x:row>
+    <x:row r="427">
+      <x:c r="A427"/>
+      <x:c r="B427"/>
+      <x:c r="C427"/>
+      <x:c r="D427"/>
+      <x:c r="E427"/>
+    </x:row>
+    <x:row r="428">
+      <x:c r="A428"/>
+      <x:c r="B428"/>
+      <x:c r="C428"/>
+      <x:c r="D428"/>
+      <x:c r="E428"/>
+    </x:row>
+    <x:row r="429">
+      <x:c r="A429"/>
+      <x:c r="B429"/>
+      <x:c r="C429"/>
+      <x:c r="D429"/>
+      <x:c r="E429"/>
+    </x:row>
+    <x:row r="430">
+      <x:c r="A430"/>
+      <x:c r="B430"/>
+      <x:c r="C430"/>
+      <x:c r="D430"/>
+      <x:c r="E430"/>
+    </x:row>
+    <x:row r="431">
+      <x:c r="A431"/>
+      <x:c r="B431"/>
+      <x:c r="C431"/>
+      <x:c r="D431"/>
+      <x:c r="E431"/>
+    </x:row>
+    <x:row r="432">
+      <x:c r="A432"/>
+      <x:c r="B432"/>
+      <x:c r="C432"/>
+      <x:c r="D432"/>
+      <x:c r="E432"/>
+    </x:row>
+    <x:row r="433">
+      <x:c r="A433"/>
+      <x:c r="B433"/>
+      <x:c r="C433"/>
+      <x:c r="D433"/>
+      <x:c r="E433"/>
+    </x:row>
+    <x:row r="434">
+      <x:c r="A434"/>
+      <x:c r="B434"/>
+      <x:c r="C434"/>
+      <x:c r="D434"/>
+      <x:c r="E434"/>
+    </x:row>
+    <x:row r="435">
+      <x:c r="A435"/>
+      <x:c r="B435"/>
+      <x:c r="C435"/>
+      <x:c r="D435"/>
+      <x:c r="E435"/>
+    </x:row>
+    <x:row r="436">
+      <x:c r="A436"/>
+      <x:c r="B436"/>
+      <x:c r="C436"/>
+      <x:c r="D436"/>
+      <x:c r="E436"/>
+    </x:row>
+    <x:row r="437">
+      <x:c r="A437"/>
+      <x:c r="B437"/>
+      <x:c r="C437"/>
+      <x:c r="D437"/>
+      <x:c r="E437"/>
+    </x:row>
+    <x:row r="438">
+      <x:c r="A438"/>
+      <x:c r="B438"/>
+      <x:c r="C438"/>
+      <x:c r="D438"/>
+      <x:c r="E438"/>
+    </x:row>
+    <x:row r="439">
+      <x:c r="A439"/>
+      <x:c r="B439"/>
+      <x:c r="C439"/>
+      <x:c r="D439"/>
+      <x:c r="E439"/>
+    </x:row>
+    <x:row r="440">
+      <x:c r="A440"/>
+      <x:c r="B440"/>
+      <x:c r="C440"/>
+      <x:c r="D440"/>
+      <x:c r="E440"/>
+    </x:row>
+    <x:row r="441">
+      <x:c r="A441"/>
+      <x:c r="B441"/>
+      <x:c r="C441"/>
+      <x:c r="D441"/>
+      <x:c r="E441"/>
+    </x:row>
+    <x:row r="442">
+      <x:c r="A442"/>
+      <x:c r="B442"/>
+      <x:c r="C442"/>
+      <x:c r="D442"/>
+      <x:c r="E442"/>
+    </x:row>
+    <x:row r="443">
+      <x:c r="A443"/>
+      <x:c r="B443"/>
+      <x:c r="C443"/>
+      <x:c r="D443"/>
+      <x:c r="E443"/>
+    </x:row>
+    <x:row r="444">
+      <x:c r="A444"/>
+      <x:c r="B444"/>
+      <x:c r="C444"/>
+      <x:c r="D444"/>
+      <x:c r="E444"/>
+    </x:row>
+    <x:row r="445">
+      <x:c r="A445"/>
+      <x:c r="B445"/>
+      <x:c r="C445"/>
+      <x:c r="D445"/>
+      <x:c r="E445"/>
+    </x:row>
+    <x:row r="446">
+      <x:c r="A446"/>
+      <x:c r="B446"/>
+      <x:c r="C446"/>
+      <x:c r="D446"/>
+      <x:c r="E446"/>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447"/>
+      <x:c r="B447"/>
+      <x:c r="C447"/>
+      <x:c r="D447"/>
+      <x:c r="E447"/>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448"/>
+      <x:c r="B448"/>
+      <x:c r="C448"/>
+      <x:c r="D448"/>
+      <x:c r="E448"/>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449"/>
+      <x:c r="B449"/>
+      <x:c r="C449"/>
+      <x:c r="D449"/>
+      <x:c r="E449"/>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450"/>
+      <x:c r="B450"/>
+      <x:c r="C450"/>
+      <x:c r="D450"/>
+      <x:c r="E450"/>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451"/>
+      <x:c r="B451"/>
+      <x:c r="C451"/>
+      <x:c r="D451"/>
+      <x:c r="E451"/>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452"/>
+      <x:c r="B452"/>
+      <x:c r="C452"/>
+      <x:c r="D452"/>
+      <x:c r="E452"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/WaveGroup.xlsx
+++ b/design/tables/WaveGroup.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="R167acce547174077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="R4a1d6b2f3f454f86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6413,10 +6413,10 @@
     </x:row>
     <x:row r="359" ht="48" hidden="0" customHeight="1">
       <x:c r="A359" s="14" t="n">
-        <x:v>448</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B359" s="14" t="n">
-        <x:v>2006</x:v>
+        <x:v>2101</x:v>
       </x:c>
       <x:c r="C359" s="14" t="n">
         <x:v>1</x:v>
@@ -6425,15 +6425,15 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E359" s="14" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="360" ht="48" customHeight="1">
       <x:c r="A360" s="16" t="n">
-        <x:v>449</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B360" s="16" t="n">
-        <x:v>2006</x:v>
+        <x:v>2101</x:v>
       </x:c>
       <x:c r="C360" s="16" t="n">
         <x:v>2</x:v>
@@ -6447,10 +6447,10 @@
     </x:row>
     <x:row r="361" ht="48" customHeight="1">
       <x:c r="A361" s="16" t="n">
-        <x:v>450</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B361" s="16" t="n">
-        <x:v>2007</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="C361" s="16" t="n">
         <x:v>1</x:v>
@@ -6459,32 +6459,32 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E361" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="362" ht="48" customHeight="1">
       <x:c r="A362" s="16" t="n">
-        <x:v>451</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B362" s="16" t="n">
-        <x:v>2007</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="C362" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D362" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E362" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="363" ht="48" customHeight="1">
       <x:c r="A363" s="16" t="n">
-        <x:v>452</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B363" s="16" t="n">
-        <x:v>2008</x:v>
+        <x:v>2103</x:v>
       </x:c>
       <x:c r="C363" s="16" t="n">
         <x:v>1</x:v>
@@ -6493,15 +6493,15 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E363" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="364" ht="48" customHeight="1">
       <x:c r="A364" s="16" t="n">
-        <x:v>453</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B364" s="16" t="n">
-        <x:v>2008</x:v>
+        <x:v>2103</x:v>
       </x:c>
       <x:c r="C364" s="16" t="n">
         <x:v>2</x:v>
@@ -6510,72 +6510,72 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E364" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="365" ht="48" customHeight="1">
       <x:c r="A365" s="16" t="n">
-        <x:v>454</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B365" s="16" t="n">
-        <x:v>2009</x:v>
+        <x:v>2103</x:v>
       </x:c>
       <x:c r="C365" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D365" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="E365" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="366" ht="48" customHeight="1">
       <x:c r="A366" s="16" t="n">
-        <x:v>455</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B366" s="16" t="n">
-        <x:v>2009</x:v>
+        <x:v>2104</x:v>
       </x:c>
       <x:c r="C366" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D366" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E366" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="367" ht="48" customHeight="1">
       <x:c r="A367" s="16" t="n">
-        <x:v>456</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B367" s="16" t="n">
-        <x:v>2009</x:v>
+        <x:v>2104</x:v>
       </x:c>
       <x:c r="C367" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D367" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E367" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="368" ht="48" customHeight="1">
       <x:c r="A368" s="16" t="n">
-        <x:v>457</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B368" s="16" t="n">
-        <x:v>2010</x:v>
+        <x:v>2104</x:v>
       </x:c>
       <x:c r="C368" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D368" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E368" s="16" t="n">
         <x:v>3</x:v>
@@ -6583,84 +6583,84 @@
     </x:row>
     <x:row r="369" ht="48" customHeight="1">
       <x:c r="A369" s="16" t="n">
-        <x:v>458</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B369" s="16" t="n">
-        <x:v>2010</x:v>
+        <x:v>2105</x:v>
       </x:c>
       <x:c r="C369" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D369" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E369" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="370" ht="48" customHeight="1">
       <x:c r="A370" s="16" t="n">
-        <x:v>459</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B370" s="16" t="n">
-        <x:v>2010</x:v>
+        <x:v>2105</x:v>
       </x:c>
       <x:c r="C370" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D370" s="16" t="str">
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E370" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="48" customHeight="1">
       <x:c r="A371" s="16" t="n">
-        <x:v>460</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B371" s="16" t="n">
-        <x:v>2011</x:v>
+        <x:v>2105</x:v>
       </x:c>
       <x:c r="C371" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D371" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>postmaster</x:v>
       </x:c>
       <x:c r="E371" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="372" ht="48" customHeight="1">
       <x:c r="A372" s="16" t="n">
-        <x:v>461</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B372" s="16" t="n">
-        <x:v>2011</x:v>
+        <x:v>2106</x:v>
       </x:c>
       <x:c r="C372" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D372" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E372" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="373" ht="48" customHeight="1">
       <x:c r="A373" s="16" t="n">
-        <x:v>462</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B373" s="16" t="n">
-        <x:v>2012</x:v>
+        <x:v>2106</x:v>
       </x:c>
       <x:c r="C373" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D373" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>runner</x:v>
       </x:c>
       <x:c r="E373" s="16" t="n">
         <x:v>4</x:v>
@@ -6668,870 +6668,640 @@
     </x:row>
     <x:row r="374" ht="48" customHeight="1">
       <x:c r="A374" s="16" t="n">
-        <x:v>463</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B374" s="16" t="n">
-        <x:v>2012</x:v>
+        <x:v>2106</x:v>
       </x:c>
       <x:c r="C374" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D374" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="E374" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="375" ht="48" customHeight="1">
       <x:c r="A375" s="16" t="n">
-        <x:v>464</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B375" s="16" t="n">
-        <x:v>2012</x:v>
+        <x:v>2107</x:v>
       </x:c>
       <x:c r="C375" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D375" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E375" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="376" ht="48" customHeight="1">
       <x:c r="A376" s="16" t="n">
-        <x:v>465</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B376" s="16" t="n">
-        <x:v>2013</x:v>
+        <x:v>2107</x:v>
       </x:c>
       <x:c r="C376" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D376" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E376" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="377" ht="48" customHeight="1">
       <x:c r="A377" s="16" t="n">
-        <x:v>466</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B377" s="16" t="n">
-        <x:v>2013</x:v>
+        <x:v>2108</x:v>
       </x:c>
       <x:c r="C377" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D377" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E377" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="378" ht="48" customHeight="1">
       <x:c r="A378" s="16" t="n">
-        <x:v>467</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B378" s="16" t="n">
-        <x:v>2013</x:v>
+        <x:v>2108</x:v>
       </x:c>
       <x:c r="C378" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D378" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="E378" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="379" ht="48" customHeight="1">
       <x:c r="A379" s="16" t="n">
-        <x:v>468</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B379" s="16" t="n">
-        <x:v>2014</x:v>
+        <x:v>2108</x:v>
       </x:c>
       <x:c r="C379" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D379" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>tank</x:v>
       </x:c>
       <x:c r="E379" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="380" ht="48" customHeight="1">
       <x:c r="A380" s="16" t="n">
-        <x:v>469</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B380" s="16" t="n">
-        <x:v>2014</x:v>
+        <x:v>2109</x:v>
       </x:c>
       <x:c r="C380" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D380" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>runner</x:v>
       </x:c>
       <x:c r="E380" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="381" ht="48" customHeight="1">
       <x:c r="A381" s="16" t="n">
-        <x:v>470</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B381" s="16" t="n">
-        <x:v>2014</x:v>
+        <x:v>2109</x:v>
       </x:c>
       <x:c r="C381" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D381" s="16" t="str">
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E381" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="382" ht="48" customHeight="1">
       <x:c r="A382" s="16" t="n">
-        <x:v>471</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B382" s="16" t="n">
-        <x:v>2015</x:v>
+        <x:v>2109</x:v>
       </x:c>
       <x:c r="C382" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D382" s="16" t="str">
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E382" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="383" ht="48" customHeight="1">
       <x:c r="A383" s="16" t="n">
-        <x:v>472</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B383" s="16" t="n">
-        <x:v>2015</x:v>
+        <x:v>2110</x:v>
       </x:c>
       <x:c r="C383" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D383" s="16" t="str">
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E383" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="384" ht="48" customHeight="1">
       <x:c r="A384" s="16" t="n">
-        <x:v>473</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B384" s="16" t="n">
-        <x:v>2015</x:v>
+        <x:v>2110</x:v>
       </x:c>
       <x:c r="C384" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D384" s="16" t="str">
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E384" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="385" ht="48" customHeight="1">
       <x:c r="A385" s="16" t="n">
-        <x:v>474</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B385" s="16" t="n">
-        <x:v>2016</x:v>
+        <x:v>2110</x:v>
       </x:c>
       <x:c r="C385" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D385" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>lantern</x:v>
       </x:c>
       <x:c r="E385" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="386" ht="48" customHeight="1">
       <x:c r="A386" s="16" t="n">
-        <x:v>475</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B386" s="16" t="n">
-        <x:v>2016</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="C386" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D386" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="E386" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="387" ht="48" customHeight="1">
       <x:c r="A387" s="16" t="n">
-        <x:v>476</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B387" s="16" t="n">
-        <x:v>2016</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="C387" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D387" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>runner</x:v>
       </x:c>
       <x:c r="E387" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="388" ht="48" customHeight="1">
       <x:c r="A388" s="16" t="n">
-        <x:v>477</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B388" s="16" t="n">
-        <x:v>2017</x:v>
+        <x:v>2111</x:v>
       </x:c>
       <x:c r="C388" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D388" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>tank</x:v>
       </x:c>
       <x:c r="E388" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="389" ht="48" customHeight="1">
       <x:c r="A389" s="16" t="n">
-        <x:v>478</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B389" s="16" t="n">
-        <x:v>2017</x:v>
+        <x:v>2112</x:v>
       </x:c>
       <x:c r="C389" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D389" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E389" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="390" ht="48" customHeight="1">
       <x:c r="A390" s="16" t="n">
-        <x:v>479</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B390" s="16" t="n">
-        <x:v>2018</x:v>
+        <x:v>2112</x:v>
       </x:c>
       <x:c r="C390" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D390" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E390" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="391" ht="48" customHeight="1">
       <x:c r="A391" s="16" t="n">
-        <x:v>480</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B391" s="16" t="n">
-        <x:v>2018</x:v>
+        <x:v>2112</x:v>
       </x:c>
       <x:c r="C391" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D391" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E391" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="392" ht="48" customHeight="1">
       <x:c r="A392" s="16" t="n">
-        <x:v>481</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B392" s="16" t="n">
-        <x:v>2018</x:v>
+        <x:v>2113</x:v>
       </x:c>
       <x:c r="C392" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D392" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>tank</x:v>
       </x:c>
       <x:c r="E392" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="393" ht="48" customHeight="1">
       <x:c r="A393" s="16" t="n">
-        <x:v>482</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B393" s="16" t="n">
-        <x:v>2019</x:v>
+        <x:v>2113</x:v>
       </x:c>
       <x:c r="C393" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D393" s="16" t="str">
-        <x:v>postmaster</x:v>
+        <x:v>runner</x:v>
       </x:c>
       <x:c r="E393" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="394" ht="48" customHeight="1">
       <x:c r="A394" s="16" t="n">
-        <x:v>483</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B394" s="16" t="n">
-        <x:v>2019</x:v>
+        <x:v>2113</x:v>
       </x:c>
       <x:c r="C394" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D394" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E394" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="395" ht="48" customHeight="1">
       <x:c r="A395" s="16" t="n">
-        <x:v>484</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B395" s="16" t="n">
-        <x:v>2019</x:v>
+        <x:v>2114</x:v>
       </x:c>
       <x:c r="C395" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D395" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="E395" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="396" ht="48" customHeight="1">
       <x:c r="A396" s="16" t="n">
-        <x:v>485</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B396" s="16" t="n">
-        <x:v>2019</x:v>
+        <x:v>2114</x:v>
       </x:c>
       <x:c r="C396" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D396" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E396" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="397" ht="48" customHeight="1">
       <x:c r="A397" s="16" t="n">
-        <x:v>486</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B397" s="16" t="n">
-        <x:v>2020</x:v>
+        <x:v>2114</x:v>
       </x:c>
       <x:c r="C397" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D397" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>tank</x:v>
       </x:c>
       <x:c r="E397" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="398" ht="48" customHeight="1">
       <x:c r="A398" s="16" t="n">
-        <x:v>487</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B398" s="16" t="n">
-        <x:v>2020</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="C398" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D398" s="16" t="str">
-        <x:v>swift</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E398" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="399" ht="48" customHeight="1">
       <x:c r="A399" s="16" t="n">
-        <x:v>488</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B399" s="16" t="n">
-        <x:v>2020</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="C399" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D399" s="16" t="str">
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E399" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="400" ht="48" customHeight="1">
       <x:c r="A400" s="16" t="n">
-        <x:v>489</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B400" s="16" t="n">
-        <x:v>2020</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="C400" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D400" s="16" t="str">
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E400" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="401" ht="48" customHeight="1">
       <x:c r="A401" s="16" t="n">
-        <x:v>490</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B401" s="16" t="n">
-        <x:v>2021</x:v>
+        <x:v>2115</x:v>
       </x:c>
       <x:c r="C401" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D401" s="16" t="str">
-        <x:v>normal</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E401" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="402" ht="48" customHeight="1">
-      <x:c r="A402" s="16" t="n">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="B402" s="16" t="n">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c r="C402" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D402" s="16" t="str">
-        <x:v>swift</x:v>
-      </x:c>
-      <x:c r="E402" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A402" s="16"/>
+      <x:c r="B402" s="16"/>
+      <x:c r="C402" s="16"/>
+      <x:c r="D402" s="16"/>
+      <x:c r="E402" s="16"/>
     </x:row>
     <x:row r="403" ht="48" customHeight="1">
-      <x:c r="A403" s="16" t="n">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="B403" s="16" t="n">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c r="C403" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D403" s="16" t="str">
-        <x:v>shield</x:v>
-      </x:c>
-      <x:c r="E403" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A403" s="16"/>
+      <x:c r="B403" s="16"/>
+      <x:c r="C403" s="16"/>
+      <x:c r="D403" s="16"/>
+      <x:c r="E403" s="16"/>
     </x:row>
     <x:row r="404" ht="48" customHeight="1">
-      <x:c r="A404" s="16" t="n">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="B404" s="16" t="n">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c r="C404" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D404" s="16" t="str">
-        <x:v>runner</x:v>
-      </x:c>
-      <x:c r="E404" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A404" s="16"/>
+      <x:c r="B404" s="16"/>
+      <x:c r="C404" s="16"/>
+      <x:c r="D404" s="16"/>
+      <x:c r="E404" s="16"/>
     </x:row>
     <x:row r="405" ht="48" customHeight="1">
-      <x:c r="A405" s="16" t="n">
-        <x:v>494</x:v>
-      </x:c>
-      <x:c r="B405" s="16" t="n">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="C405" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D405" s="16" t="str">
-        <x:v>normal</x:v>
-      </x:c>
-      <x:c r="E405" s="16" t="n">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A405" s="16"/>
+      <x:c r="B405" s="16"/>
+      <x:c r="C405" s="16"/>
+      <x:c r="D405" s="16"/>
+      <x:c r="E405" s="16"/>
     </x:row>
     <x:row r="406" ht="48" customHeight="1">
-      <x:c r="A406" s="16" t="n">
-        <x:v>495</x:v>
-      </x:c>
-      <x:c r="B406" s="16" t="n">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="C406" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D406" s="16" t="str">
-        <x:v>swift</x:v>
-      </x:c>
-      <x:c r="E406" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A406" s="16"/>
+      <x:c r="B406" s="16"/>
+      <x:c r="C406" s="16"/>
+      <x:c r="D406" s="16"/>
+      <x:c r="E406" s="16"/>
     </x:row>
     <x:row r="407" ht="48" customHeight="1">
-      <x:c r="A407" s="16" t="n">
-        <x:v>496</x:v>
-      </x:c>
-      <x:c r="B407" s="16" t="n">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="C407" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D407" s="16" t="str">
-        <x:v>shield</x:v>
-      </x:c>
-      <x:c r="E407" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A407" s="16"/>
+      <x:c r="B407" s="16"/>
+      <x:c r="C407" s="16"/>
+      <x:c r="D407" s="16"/>
+      <x:c r="E407" s="16"/>
     </x:row>
     <x:row r="408" ht="48" customHeight="1">
-      <x:c r="A408" s="16" t="n">
-        <x:v>497</x:v>
-      </x:c>
-      <x:c r="B408" s="16" t="n">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="C408" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D408" s="16" t="str">
-        <x:v>runner</x:v>
-      </x:c>
-      <x:c r="E408" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A408" s="16"/>
+      <x:c r="B408" s="16"/>
+      <x:c r="C408" s="16"/>
+      <x:c r="D408" s="16"/>
+      <x:c r="E408" s="16"/>
     </x:row>
     <x:row r="409" ht="48" customHeight="1">
-      <x:c r="A409" s="16" t="n">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="B409" s="16" t="n">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c r="C409" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D409" s="16" t="str">
-        <x:v>normal</x:v>
-      </x:c>
-      <x:c r="E409" s="16" t="n">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A409" s="16"/>
+      <x:c r="B409" s="16"/>
+      <x:c r="C409" s="16"/>
+      <x:c r="D409" s="16"/>
+      <x:c r="E409" s="16"/>
     </x:row>
     <x:row r="410" ht="48" customHeight="1">
-      <x:c r="A410" s="16" t="n">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="B410" s="16" t="n">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c r="C410" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D410" s="16" t="str">
-        <x:v>swift</x:v>
-      </x:c>
-      <x:c r="E410" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A410" s="16"/>
+      <x:c r="B410" s="16"/>
+      <x:c r="C410" s="16"/>
+      <x:c r="D410" s="16"/>
+      <x:c r="E410" s="16"/>
     </x:row>
     <x:row r="411" ht="48" customHeight="1">
-      <x:c r="A411" s="16" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="B411" s="16" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="C411" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D411" s="16" t="str">
-        <x:v>normal</x:v>
-      </x:c>
-      <x:c r="E411" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="A411" s="16"/>
+      <x:c r="B411" s="16"/>
+      <x:c r="C411" s="16"/>
+      <x:c r="D411" s="16"/>
+      <x:c r="E411" s="16"/>
     </x:row>
     <x:row r="412" ht="48" customHeight="1">
-      <x:c r="A412" s="16" t="n">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="B412" s="16" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="C412" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D412" s="16" t="str">
-        <x:v>swift</x:v>
-      </x:c>
-      <x:c r="E412" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A412" s="16"/>
+      <x:c r="B412" s="16"/>
+      <x:c r="C412" s="16"/>
+      <x:c r="D412" s="16"/>
+      <x:c r="E412" s="16"/>
     </x:row>
     <x:row r="413" ht="48" customHeight="1">
-      <x:c r="A413" s="16" t="n">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="B413" s="16" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="C413" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D413" s="16" t="str">
-        <x:v>shield</x:v>
-      </x:c>
-      <x:c r="E413" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="A413" s="16"/>
+      <x:c r="B413" s="16"/>
+      <x:c r="C413" s="16"/>
+      <x:c r="D413" s="16"/>
+      <x:c r="E413" s="16"/>
     </x:row>
     <x:row r="414" ht="48" customHeight="1">
-      <x:c r="A414" s="16" t="n">
-        <x:v>503</x:v>
-      </x:c>
-      <x:c r="B414" s="16" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="C414" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D414" s="16" t="str">
-        <x:v>runner</x:v>
-      </x:c>
-      <x:c r="E414" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A414" s="16"/>
+      <x:c r="B414" s="16"/>
+      <x:c r="C414" s="16"/>
+      <x:c r="D414" s="16"/>
+      <x:c r="E414" s="16"/>
     </x:row>
     <x:row r="415" ht="48" customHeight="1">
-      <x:c r="A415" s="16" t="n">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="B415" s="16" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="C415" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D415" s="16" t="str">
-        <x:v>normal</x:v>
-      </x:c>
-      <x:c r="E415" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="A415" s="16"/>
+      <x:c r="B415" s="16"/>
+      <x:c r="C415" s="16"/>
+      <x:c r="D415" s="16"/>
+      <x:c r="E415" s="16"/>
     </x:row>
     <x:row r="416" ht="48" customHeight="1">
-      <x:c r="A416" s="16" t="n">
-        <x:v>505</x:v>
-      </x:c>
-      <x:c r="B416" s="16" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="C416" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D416" s="16" t="str">
-        <x:v>swift</x:v>
-      </x:c>
-      <x:c r="E416" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A416" s="16"/>
+      <x:c r="B416" s="16"/>
+      <x:c r="C416" s="16"/>
+      <x:c r="D416" s="16"/>
+      <x:c r="E416" s="16"/>
     </x:row>
     <x:row r="417" ht="48" customHeight="1">
-      <x:c r="A417" s="16" t="n">
-        <x:v>506</x:v>
-      </x:c>
-      <x:c r="B417" s="16" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="C417" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D417" s="16" t="str">
-        <x:v>shield</x:v>
-      </x:c>
-      <x:c r="E417" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="A417" s="16"/>
+      <x:c r="B417" s="16"/>
+      <x:c r="C417" s="16"/>
+      <x:c r="D417" s="16"/>
+      <x:c r="E417" s="16"/>
     </x:row>
     <x:row r="418" ht="48" customHeight="1">
-      <x:c r="A418" s="16" t="n">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="B418" s="16" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="C418" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D418" s="16" t="str">
-        <x:v>runner</x:v>
-      </x:c>
-      <x:c r="E418" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A418" s="16"/>
+      <x:c r="B418" s="16"/>
+      <x:c r="C418" s="16"/>
+      <x:c r="D418" s="16"/>
+      <x:c r="E418" s="16"/>
     </x:row>
     <x:row r="419" ht="48" customHeight="1">
-      <x:c r="A419" s="16" t="n">
-        <x:v>508</x:v>
-      </x:c>
-      <x:c r="B419" s="16" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="C419" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D419" s="16" t="str">
-        <x:v>clock</x:v>
-      </x:c>
-      <x:c r="E419" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A419" s="16"/>
+      <x:c r="B419" s="16"/>
+      <x:c r="C419" s="16"/>
+      <x:c r="D419" s="16"/>
+      <x:c r="E419" s="16"/>
     </x:row>
     <x:row r="420" ht="48" customHeight="1">
-      <x:c r="A420" s="16" t="n">
-        <x:v>509</x:v>
-      </x:c>
-      <x:c r="B420" s="16" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="C420" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D420" s="16" t="str">
-        <x:v>postmaster</x:v>
-      </x:c>
-      <x:c r="E420" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A420" s="16"/>
+      <x:c r="B420" s="16"/>
+      <x:c r="C420" s="16"/>
+      <x:c r="D420" s="16"/>
+      <x:c r="E420" s="16"/>
     </x:row>
     <x:row r="421" ht="48" customHeight="1">
-      <x:c r="A421" s="16" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="B421" s="16" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="C421" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D421" s="16" t="str">
-        <x:v>normal</x:v>
-      </x:c>
-      <x:c r="E421" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="A421" s="16"/>
+      <x:c r="B421" s="16"/>
+      <x:c r="C421" s="16"/>
+      <x:c r="D421" s="16"/>
+      <x:c r="E421" s="16"/>
     </x:row>
     <x:row r="422" ht="48" customHeight="1">
-      <x:c r="A422" s="16" t="n">
-        <x:v>511</x:v>
-      </x:c>
-      <x:c r="B422" s="16" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="C422" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D422" s="16" t="str">
-        <x:v>swift</x:v>
-      </x:c>
-      <x:c r="E422" s="16" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A422" s="16"/>
+      <x:c r="B422" s="16"/>
+      <x:c r="C422" s="16"/>
+      <x:c r="D422" s="16"/>
+      <x:c r="E422" s="16"/>
     </x:row>
     <x:row r="423" ht="48" customHeight="1">
-      <x:c r="A423" s="16" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="B423" s="16" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="C423" s="16" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D423" s="16" t="str">
-        <x:v>shield</x:v>
-      </x:c>
-      <x:c r="E423" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="A423" s="16"/>
+      <x:c r="B423" s="16"/>
+      <x:c r="C423" s="16"/>
+      <x:c r="D423" s="16"/>
+      <x:c r="E423" s="16"/>
     </x:row>
     <x:row r="424" ht="48" customHeight="1">
-      <x:c r="A424" s="16" t="n">
-        <x:v>513</x:v>
-      </x:c>
-      <x:c r="B424" s="16" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="C424" s="16" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D424" s="16" t="str">
-        <x:v>runner</x:v>
-      </x:c>
-      <x:c r="E424" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A424" s="16"/>
+      <x:c r="B424" s="16"/>
+      <x:c r="C424" s="16"/>
+      <x:c r="D424" s="16"/>
+      <x:c r="E424" s="16"/>
     </x:row>
     <x:row r="425">
       <x:c r="A425"/>

--- a/design/tables/WaveGroup.xlsx
+++ b/design/tables/WaveGroup.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="R4a1d6b2f3f454f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="R05a15f7379874a69"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7143,361 +7143,3591 @@
       </x:c>
     </x:row>
     <x:row r="402" ht="48" customHeight="1">
-      <x:c r="A402" s="16"/>
-      <x:c r="B402" s="16"/>
-      <x:c r="C402" s="16"/>
-      <x:c r="D402" s="16"/>
-      <x:c r="E402" s="16"/>
+      <x:c r="A402" s="16" t="n">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B402" s="16" t="n">
+        <x:v>2201</x:v>
+      </x:c>
+      <x:c r="C402" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D402" s="16" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E402" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="403" ht="48" customHeight="1">
-      <x:c r="A403" s="16"/>
-      <x:c r="B403" s="16"/>
-      <x:c r="C403" s="16"/>
-      <x:c r="D403" s="16"/>
-      <x:c r="E403" s="16"/>
+      <x:c r="A403" s="16" t="n">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B403" s="16" t="n">
+        <x:v>2201</x:v>
+      </x:c>
+      <x:c r="C403" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D403" s="16" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E403" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="404" ht="48" customHeight="1">
-      <x:c r="A404" s="16"/>
-      <x:c r="B404" s="16"/>
-      <x:c r="C404" s="16"/>
-      <x:c r="D404" s="16"/>
-      <x:c r="E404" s="16"/>
+      <x:c r="A404" s="16" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B404" s="16" t="n">
+        <x:v>2202</x:v>
+      </x:c>
+      <x:c r="C404" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D404" s="16" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E404" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="405" ht="48" customHeight="1">
-      <x:c r="A405" s="16"/>
-      <x:c r="B405" s="16"/>
-      <x:c r="C405" s="16"/>
-      <x:c r="D405" s="16"/>
-      <x:c r="E405" s="16"/>
+      <x:c r="A405" s="16" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B405" s="16" t="n">
+        <x:v>2202</x:v>
+      </x:c>
+      <x:c r="C405" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D405" s="16" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E405" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="406" ht="48" customHeight="1">
-      <x:c r="A406" s="16"/>
-      <x:c r="B406" s="16"/>
-      <x:c r="C406" s="16"/>
-      <x:c r="D406" s="16"/>
-      <x:c r="E406" s="16"/>
+      <x:c r="A406" s="16" t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B406" s="16" t="n">
+        <x:v>2202</x:v>
+      </x:c>
+      <x:c r="C406" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D406" s="16" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E406" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="407" ht="48" customHeight="1">
-      <x:c r="A407" s="16"/>
-      <x:c r="B407" s="16"/>
-      <x:c r="C407" s="16"/>
-      <x:c r="D407" s="16"/>
-      <x:c r="E407" s="16"/>
+      <x:c r="A407" s="16" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B407" s="16" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="C407" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D407" s="16" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E407" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="408" ht="48" customHeight="1">
-      <x:c r="A408" s="16"/>
-      <x:c r="B408" s="16"/>
-      <x:c r="C408" s="16"/>
-      <x:c r="D408" s="16"/>
-      <x:c r="E408" s="16"/>
+      <x:c r="A408" s="16" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B408" s="16" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="C408" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D408" s="16" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E408" s="16" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="409" ht="48" customHeight="1">
-      <x:c r="A409" s="16"/>
-      <x:c r="B409" s="16"/>
-      <x:c r="C409" s="16"/>
-      <x:c r="D409" s="16"/>
-      <x:c r="E409" s="16"/>
+      <x:c r="A409" s="16" t="n">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B409" s="16" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="C409" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D409" s="16" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E409" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="410" ht="48" customHeight="1">
-      <x:c r="A410" s="16"/>
-      <x:c r="B410" s="16"/>
-      <x:c r="C410" s="16"/>
-      <x:c r="D410" s="16"/>
-      <x:c r="E410" s="16"/>
+      <x:c r="A410" s="16" t="n">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B410" s="16" t="n">
+        <x:v>2204</x:v>
+      </x:c>
+      <x:c r="C410" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D410" s="16" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E410" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="411" ht="48" customHeight="1">
-      <x:c r="A411" s="16"/>
-      <x:c r="B411" s="16"/>
-      <x:c r="C411" s="16"/>
-      <x:c r="D411" s="16"/>
-      <x:c r="E411" s="16"/>
+      <x:c r="A411" s="16" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B411" s="16" t="n">
+        <x:v>2204</x:v>
+      </x:c>
+      <x:c r="C411" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D411" s="16" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E411" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="412" ht="48" customHeight="1">
-      <x:c r="A412" s="16"/>
-      <x:c r="B412" s="16"/>
-      <x:c r="C412" s="16"/>
-      <x:c r="D412" s="16"/>
-      <x:c r="E412" s="16"/>
+      <x:c r="A412" s="16" t="n">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B412" s="16" t="n">
+        <x:v>2204</x:v>
+      </x:c>
+      <x:c r="C412" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D412" s="16" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E412" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="413" ht="48" customHeight="1">
-      <x:c r="A413" s="16"/>
-      <x:c r="B413" s="16"/>
-      <x:c r="C413" s="16"/>
-      <x:c r="D413" s="16"/>
-      <x:c r="E413" s="16"/>
+      <x:c r="A413" s="16" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B413" s="16" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="C413" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D413" s="16" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E413" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="414" ht="48" customHeight="1">
-      <x:c r="A414" s="16"/>
-      <x:c r="B414" s="16"/>
-      <x:c r="C414" s="16"/>
-      <x:c r="D414" s="16"/>
-      <x:c r="E414" s="16"/>
+      <x:c r="A414" s="16" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B414" s="16" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="C414" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D414" s="16" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E414" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="415" ht="48" customHeight="1">
-      <x:c r="A415" s="16"/>
-      <x:c r="B415" s="16"/>
-      <x:c r="C415" s="16"/>
-      <x:c r="D415" s="16"/>
-      <x:c r="E415" s="16"/>
+      <x:c r="A415" s="16" t="n">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B415" s="16" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="C415" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D415" s="16" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E415" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="416" ht="48" customHeight="1">
-      <x:c r="A416" s="16"/>
-      <x:c r="B416" s="16"/>
-      <x:c r="C416" s="16"/>
-      <x:c r="D416" s="16"/>
-      <x:c r="E416" s="16"/>
+      <x:c r="A416" s="16" t="n">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B416" s="16" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="C416" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D416" s="16" t="str">
+        <x:v>postmaster</x:v>
+      </x:c>
+      <x:c r="E416" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="417" ht="48" customHeight="1">
-      <x:c r="A417" s="16"/>
-      <x:c r="B417" s="16"/>
-      <x:c r="C417" s="16"/>
-      <x:c r="D417" s="16"/>
-      <x:c r="E417" s="16"/>
+      <x:c r="A417" s="16" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B417" s="16" t="n">
+        <x:v>2206</x:v>
+      </x:c>
+      <x:c r="C417" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D417" s="16" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E417" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="418" ht="48" customHeight="1">
-      <x:c r="A418" s="16"/>
-      <x:c r="B418" s="16"/>
-      <x:c r="C418" s="16"/>
-      <x:c r="D418" s="16"/>
-      <x:c r="E418" s="16"/>
+      <x:c r="A418" s="16" t="n">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B418" s="16" t="n">
+        <x:v>2206</x:v>
+      </x:c>
+      <x:c r="C418" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D418" s="16" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E418" s="16" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="419" ht="48" customHeight="1">
-      <x:c r="A419" s="16"/>
-      <x:c r="B419" s="16"/>
-      <x:c r="C419" s="16"/>
-      <x:c r="D419" s="16"/>
-      <x:c r="E419" s="16"/>
+      <x:c r="A419" s="16" t="n">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B419" s="16" t="n">
+        <x:v>2206</x:v>
+      </x:c>
+      <x:c r="C419" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D419" s="16" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E419" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="420" ht="48" customHeight="1">
-      <x:c r="A420" s="16"/>
-      <x:c r="B420" s="16"/>
-      <x:c r="C420" s="16"/>
-      <x:c r="D420" s="16"/>
-      <x:c r="E420" s="16"/>
+      <x:c r="A420" s="16" t="n">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B420" s="16" t="n">
+        <x:v>2207</x:v>
+      </x:c>
+      <x:c r="C420" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D420" s="16" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E420" s="16" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="421" ht="48" customHeight="1">
-      <x:c r="A421" s="16"/>
-      <x:c r="B421" s="16"/>
-      <x:c r="C421" s="16"/>
-      <x:c r="D421" s="16"/>
-      <x:c r="E421" s="16"/>
+      <x:c r="A421" s="16" t="n">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B421" s="16" t="n">
+        <x:v>2207</x:v>
+      </x:c>
+      <x:c r="C421" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D421" s="16" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E421" s="16" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="422" ht="48" customHeight="1">
-      <x:c r="A422" s="16"/>
-      <x:c r="B422" s="16"/>
-      <x:c r="C422" s="16"/>
-      <x:c r="D422" s="16"/>
-      <x:c r="E422" s="16"/>
+      <x:c r="A422" s="16" t="n">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B422" s="16" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="C422" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D422" s="16" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E422" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="423" ht="48" customHeight="1">
-      <x:c r="A423" s="16"/>
-      <x:c r="B423" s="16"/>
-      <x:c r="C423" s="16"/>
-      <x:c r="D423" s="16"/>
-      <x:c r="E423" s="16"/>
+      <x:c r="A423" s="16" t="n">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B423" s="16" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="C423" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D423" s="16" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E423" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="424" ht="48" customHeight="1">
-      <x:c r="A424" s="16"/>
-      <x:c r="B424" s="16"/>
-      <x:c r="C424" s="16"/>
-      <x:c r="D424" s="16"/>
-      <x:c r="E424" s="16"/>
+      <x:c r="A424" s="16" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B424" s="16" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="C424" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D424" s="16" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E424" s="16" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="425">
-      <x:c r="A425"/>
-      <x:c r="B425"/>
-      <x:c r="C425"/>
-      <x:c r="D425"/>
-      <x:c r="E425"/>
+      <x:c r="A425" t="n">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B425" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="C425" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D425" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E425" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="426">
-      <x:c r="A426"/>
-      <x:c r="B426"/>
-      <x:c r="C426"/>
-      <x:c r="D426"/>
-      <x:c r="E426"/>
+      <x:c r="A426" t="n">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B426" t="n">
+        <x:v>2209</x:v>
+      </x:c>
+      <x:c r="C426" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D426" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E426" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="427">
-      <x:c r="A427"/>
-      <x:c r="B427"/>
-      <x:c r="C427"/>
-      <x:c r="D427"/>
-      <x:c r="E427"/>
+      <x:c r="A427" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B427" t="n">
+        <x:v>2209</x:v>
+      </x:c>
+      <x:c r="C427" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D427" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E427" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="428">
-      <x:c r="A428"/>
-      <x:c r="B428"/>
-      <x:c r="C428"/>
-      <x:c r="D428"/>
-      <x:c r="E428"/>
+      <x:c r="A428" t="n">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B428" t="n">
+        <x:v>2209</x:v>
+      </x:c>
+      <x:c r="C428" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D428" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E428" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="429">
-      <x:c r="A429"/>
-      <x:c r="B429"/>
-      <x:c r="C429"/>
-      <x:c r="D429"/>
-      <x:c r="E429"/>
+      <x:c r="A429" t="n">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B429" t="n">
+        <x:v>2210</x:v>
+      </x:c>
+      <x:c r="C429" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D429" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E429" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="430">
-      <x:c r="A430"/>
-      <x:c r="B430"/>
-      <x:c r="C430"/>
-      <x:c r="D430"/>
-      <x:c r="E430"/>
+      <x:c r="A430" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B430" t="n">
+        <x:v>2210</x:v>
+      </x:c>
+      <x:c r="C430" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D430" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E430" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="431">
-      <x:c r="A431"/>
-      <x:c r="B431"/>
-      <x:c r="C431"/>
-      <x:c r="D431"/>
-      <x:c r="E431"/>
+      <x:c r="A431" t="n">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B431" t="n">
+        <x:v>2210</x:v>
+      </x:c>
+      <x:c r="C431" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D431" t="str">
+        <x:v>lantern</x:v>
+      </x:c>
+      <x:c r="E431" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="432">
-      <x:c r="A432"/>
-      <x:c r="B432"/>
-      <x:c r="C432"/>
-      <x:c r="D432"/>
-      <x:c r="E432"/>
+      <x:c r="A432" t="n">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B432" t="n">
+        <x:v>2211</x:v>
+      </x:c>
+      <x:c r="C432" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D432" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E432" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="433">
-      <x:c r="A433"/>
-      <x:c r="B433"/>
-      <x:c r="C433"/>
-      <x:c r="D433"/>
-      <x:c r="E433"/>
+      <x:c r="A433" t="n">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B433" t="n">
+        <x:v>2211</x:v>
+      </x:c>
+      <x:c r="C433" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D433" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E433" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="434">
-      <x:c r="A434"/>
-      <x:c r="B434"/>
-      <x:c r="C434"/>
-      <x:c r="D434"/>
-      <x:c r="E434"/>
+      <x:c r="A434" t="n">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B434" t="n">
+        <x:v>2211</x:v>
+      </x:c>
+      <x:c r="C434" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D434" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E434" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="435">
-      <x:c r="A435"/>
-      <x:c r="B435"/>
-      <x:c r="C435"/>
-      <x:c r="D435"/>
-      <x:c r="E435"/>
+      <x:c r="A435" t="n">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B435" t="n">
+        <x:v>2212</x:v>
+      </x:c>
+      <x:c r="C435" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D435" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E435" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="436">
-      <x:c r="A436"/>
-      <x:c r="B436"/>
-      <x:c r="C436"/>
-      <x:c r="D436"/>
-      <x:c r="E436"/>
+      <x:c r="A436" t="n">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B436" t="n">
+        <x:v>2212</x:v>
+      </x:c>
+      <x:c r="C436" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D436" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E436" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="437">
-      <x:c r="A437"/>
-      <x:c r="B437"/>
-      <x:c r="C437"/>
-      <x:c r="D437"/>
-      <x:c r="E437"/>
+      <x:c r="A437" t="n">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B437" t="n">
+        <x:v>2212</x:v>
+      </x:c>
+      <x:c r="C437" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D437" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E437" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="438">
-      <x:c r="A438"/>
-      <x:c r="B438"/>
-      <x:c r="C438"/>
-      <x:c r="D438"/>
-      <x:c r="E438"/>
+      <x:c r="A438" t="n">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B438" t="n">
+        <x:v>2212</x:v>
+      </x:c>
+      <x:c r="C438" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D438" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E438" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="439">
-      <x:c r="A439"/>
-      <x:c r="B439"/>
-      <x:c r="C439"/>
-      <x:c r="D439"/>
-      <x:c r="E439"/>
+      <x:c r="A439" t="n">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B439" t="n">
+        <x:v>2213</x:v>
+      </x:c>
+      <x:c r="C439" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D439" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E439" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="440">
-      <x:c r="A440"/>
-      <x:c r="B440"/>
-      <x:c r="C440"/>
-      <x:c r="D440"/>
-      <x:c r="E440"/>
+      <x:c r="A440" t="n">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B440" t="n">
+        <x:v>2213</x:v>
+      </x:c>
+      <x:c r="C440" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D440" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E440" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="441">
-      <x:c r="A441"/>
-      <x:c r="B441"/>
-      <x:c r="C441"/>
-      <x:c r="D441"/>
-      <x:c r="E441"/>
+      <x:c r="A441" t="n">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B441" t="n">
+        <x:v>2213</x:v>
+      </x:c>
+      <x:c r="C441" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D441" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E441" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="442">
-      <x:c r="A442"/>
-      <x:c r="B442"/>
-      <x:c r="C442"/>
-      <x:c r="D442"/>
-      <x:c r="E442"/>
+      <x:c r="A442" t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B442" t="n">
+        <x:v>2214</x:v>
+      </x:c>
+      <x:c r="C442" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D442" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E442" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="443">
-      <x:c r="A443"/>
-      <x:c r="B443"/>
-      <x:c r="C443"/>
-      <x:c r="D443"/>
-      <x:c r="E443"/>
+      <x:c r="A443" t="n">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B443" t="n">
+        <x:v>2214</x:v>
+      </x:c>
+      <x:c r="C443" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D443" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E443" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="444">
-      <x:c r="A444"/>
-      <x:c r="B444"/>
-      <x:c r="C444"/>
-      <x:c r="D444"/>
-      <x:c r="E444"/>
+      <x:c r="A444" t="n">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B444" t="n">
+        <x:v>2214</x:v>
+      </x:c>
+      <x:c r="C444" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D444" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E444" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="445">
-      <x:c r="A445"/>
-      <x:c r="B445"/>
-      <x:c r="C445"/>
-      <x:c r="D445"/>
-      <x:c r="E445"/>
+      <x:c r="A445" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B445" t="n">
+        <x:v>2215</x:v>
+      </x:c>
+      <x:c r="C445" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D445" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E445" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="446">
-      <x:c r="A446"/>
-      <x:c r="B446"/>
-      <x:c r="C446"/>
-      <x:c r="D446"/>
-      <x:c r="E446"/>
+      <x:c r="A446" t="n">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B446" t="n">
+        <x:v>2215</x:v>
+      </x:c>
+      <x:c r="C446" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D446" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E446" t="n">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
     <x:row r="447">
-      <x:c r="A447"/>
-      <x:c r="B447"/>
-      <x:c r="C447"/>
-      <x:c r="D447"/>
-      <x:c r="E447"/>
+      <x:c r="A447" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B447" t="n">
+        <x:v>2215</x:v>
+      </x:c>
+      <x:c r="C447" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D447" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E447" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="448">
-      <x:c r="A448"/>
-      <x:c r="B448"/>
-      <x:c r="C448"/>
-      <x:c r="D448"/>
-      <x:c r="E448"/>
+      <x:c r="A448" t="n">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B448" t="n">
+        <x:v>2215</x:v>
+      </x:c>
+      <x:c r="C448" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D448" t="str">
+        <x:v>clock</x:v>
+      </x:c>
+      <x:c r="E448" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="449">
-      <x:c r="A449"/>
-      <x:c r="B449"/>
-      <x:c r="C449"/>
-      <x:c r="D449"/>
-      <x:c r="E449"/>
+      <x:c r="A449" t="n">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B449" t="n">
+        <x:v>2301</x:v>
+      </x:c>
+      <x:c r="C449" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D449" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E449" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="450">
-      <x:c r="A450"/>
-      <x:c r="B450"/>
-      <x:c r="C450"/>
-      <x:c r="D450"/>
-      <x:c r="E450"/>
+      <x:c r="A450" t="n">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B450" t="n">
+        <x:v>2301</x:v>
+      </x:c>
+      <x:c r="C450" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D450" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E450" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="451">
-      <x:c r="A451"/>
-      <x:c r="B451"/>
-      <x:c r="C451"/>
-      <x:c r="D451"/>
-      <x:c r="E451"/>
+      <x:c r="A451" t="n">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B451" t="n">
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="C451" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D451" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E451" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="452">
-      <x:c r="A452"/>
-      <x:c r="B452"/>
-      <x:c r="C452"/>
-      <x:c r="D452"/>
-      <x:c r="E452"/>
+      <x:c r="A452" t="n">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B452" t="n">
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="C452" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D452" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E452" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B453" t="n">
+        <x:v>2303</x:v>
+      </x:c>
+      <x:c r="C453" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D453" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E453" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B454" t="n">
+        <x:v>2303</x:v>
+      </x:c>
+      <x:c r="C454" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D454" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E454" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" t="n">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B455" t="n">
+        <x:v>2303</x:v>
+      </x:c>
+      <x:c r="C455" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D455" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E455" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" t="n">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B456" t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c r="C456" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D456" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E456" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" t="n">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B457" t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c r="C457" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D457" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E457" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" t="n">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B458" t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c r="C458" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D458" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E458" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" t="n">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B459" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="C459" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D459" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E459" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B460" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="C460" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D460" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E460" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" t="n">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B461" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="C461" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D461" t="str">
+        <x:v>chef</x:v>
+      </x:c>
+      <x:c r="E461" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" t="n">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B462" t="n">
+        <x:v>2306</x:v>
+      </x:c>
+      <x:c r="C462" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D462" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E462" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" t="n">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B463" t="n">
+        <x:v>2306</x:v>
+      </x:c>
+      <x:c r="C463" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D463" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E463" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" t="n">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B464" t="n">
+        <x:v>2307</x:v>
+      </x:c>
+      <x:c r="C464" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D464" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E464" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B465" t="n">
+        <x:v>2307</x:v>
+      </x:c>
+      <x:c r="C465" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D465" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E465" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" t="n">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B466" t="n">
+        <x:v>2308</x:v>
+      </x:c>
+      <x:c r="C466" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D466" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E466" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467">
+      <x:c r="A467" t="n">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B467" t="n">
+        <x:v>2308</x:v>
+      </x:c>
+      <x:c r="C467" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D467" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E467" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B468" t="n">
+        <x:v>2309</x:v>
+      </x:c>
+      <x:c r="C468" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D468" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E468" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469" t="n">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B469" t="n">
+        <x:v>2309</x:v>
+      </x:c>
+      <x:c r="C469" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D469" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E469" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470" t="n">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B470" t="n">
+        <x:v>2309</x:v>
+      </x:c>
+      <x:c r="C470" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D470" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E470" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B471" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="C471" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D471" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E471" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472" t="n">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B472" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="C472" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D472" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E472" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473" t="n">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B473" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="C473" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D473" t="str">
+        <x:v>lantern</x:v>
+      </x:c>
+      <x:c r="E473" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474" t="n">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="B474" t="n">
+        <x:v>2311</x:v>
+      </x:c>
+      <x:c r="C474" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D474" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E474" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475" t="n">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B475" t="n">
+        <x:v>2311</x:v>
+      </x:c>
+      <x:c r="C475" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D475" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E475" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476" t="n">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B476" t="n">
+        <x:v>2311</x:v>
+      </x:c>
+      <x:c r="C476" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D476" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E476" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477" t="n">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="B477" t="n">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="C477" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D477" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E477" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478" t="n">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B478" t="n">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="C478" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D478" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E478" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479">
+      <x:c r="A479" t="n">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B479" t="n">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="C479" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D479" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E479" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480" t="n">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B480" t="n">
+        <x:v>2313</x:v>
+      </x:c>
+      <x:c r="C480" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D480" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E480" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481" t="n">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B481" t="n">
+        <x:v>2313</x:v>
+      </x:c>
+      <x:c r="C481" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D481" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E481" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482" t="n">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B482" t="n">
+        <x:v>2313</x:v>
+      </x:c>
+      <x:c r="C482" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D482" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E482" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483" t="n">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="B483" t="n">
+        <x:v>2314</x:v>
+      </x:c>
+      <x:c r="C483" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D483" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E483" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B484" t="n">
+        <x:v>2314</x:v>
+      </x:c>
+      <x:c r="C484" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D484" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E484" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B485" t="n">
+        <x:v>2314</x:v>
+      </x:c>
+      <x:c r="C485" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D485" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E485" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486" t="n">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B486" t="n">
+        <x:v>2315</x:v>
+      </x:c>
+      <x:c r="C486" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D486" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E486" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487" t="n">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B487" t="n">
+        <x:v>2315</x:v>
+      </x:c>
+      <x:c r="C487" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D487" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E487" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488" t="n">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B488" t="n">
+        <x:v>2315</x:v>
+      </x:c>
+      <x:c r="C488" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D488" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E488" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" t="n">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B489" t="n">
+        <x:v>2315</x:v>
+      </x:c>
+      <x:c r="C489" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D489" t="str">
+        <x:v>clock</x:v>
+      </x:c>
+      <x:c r="E489" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490" t="n">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B490" t="n">
+        <x:v>2401</x:v>
+      </x:c>
+      <x:c r="C490" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D490" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E490" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" t="n">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B491" t="n">
+        <x:v>2401</x:v>
+      </x:c>
+      <x:c r="C491" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D491" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E491" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" t="n">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B492" t="n">
+        <x:v>2402</x:v>
+      </x:c>
+      <x:c r="C492" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D492" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E492" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B493" t="n">
+        <x:v>2402</x:v>
+      </x:c>
+      <x:c r="C493" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D493" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E493" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" t="n">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B494" t="n">
+        <x:v>2403</x:v>
+      </x:c>
+      <x:c r="C494" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D494" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E494" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" t="n">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B495" t="n">
+        <x:v>2403</x:v>
+      </x:c>
+      <x:c r="C495" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D495" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E495" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" t="n">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B496" t="n">
+        <x:v>2403</x:v>
+      </x:c>
+      <x:c r="C496" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D496" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E496" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" t="n">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B497" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="C497" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D497" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E497" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498" t="n">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="B498" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="C498" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D498" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E498" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499">
+      <x:c r="A499" t="n">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B499" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="C499" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D499" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E499" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500">
+      <x:c r="A500" t="n">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B500" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="C500" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D500" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E500" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501">
+      <x:c r="A501" t="n">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B501" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="C501" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D501" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E501" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502">
+      <x:c r="A502" t="n">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="B502" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="C502" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D502" t="str">
+        <x:v>chef</x:v>
+      </x:c>
+      <x:c r="E502" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503">
+      <x:c r="A503" t="n">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B503" t="n">
+        <x:v>2406</x:v>
+      </x:c>
+      <x:c r="C503" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D503" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E503" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504">
+      <x:c r="A504" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B504" t="n">
+        <x:v>2406</x:v>
+      </x:c>
+      <x:c r="C504" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D504" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E504" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505">
+      <x:c r="A505" t="n">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B505" t="n">
+        <x:v>2406</x:v>
+      </x:c>
+      <x:c r="C505" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D505" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E505" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506">
+      <x:c r="A506" t="n">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B506" t="n">
+        <x:v>2407</x:v>
+      </x:c>
+      <x:c r="C506" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D506" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E506" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507">
+      <x:c r="A507" t="n">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B507" t="n">
+        <x:v>2407</x:v>
+      </x:c>
+      <x:c r="C507" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D507" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E507" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508">
+      <x:c r="A508" t="n">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B508" t="n">
+        <x:v>2408</x:v>
+      </x:c>
+      <x:c r="C508" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D508" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E508" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509">
+      <x:c r="A509" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B509" t="n">
+        <x:v>2408</x:v>
+      </x:c>
+      <x:c r="C509" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D509" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E509" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510">
+      <x:c r="A510" t="n">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B510" t="n">
+        <x:v>2409</x:v>
+      </x:c>
+      <x:c r="C510" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D510" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E510" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511">
+      <x:c r="A511" t="n">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B511" t="n">
+        <x:v>2409</x:v>
+      </x:c>
+      <x:c r="C511" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D511" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E511" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512">
+      <x:c r="A512" t="n">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B512" t="n">
+        <x:v>2409</x:v>
+      </x:c>
+      <x:c r="C512" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D512" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E512" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513">
+      <x:c r="A513" t="n">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B513" t="n">
+        <x:v>2410</x:v>
+      </x:c>
+      <x:c r="C513" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D513" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E513" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514">
+      <x:c r="A514" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B514" t="n">
+        <x:v>2410</x:v>
+      </x:c>
+      <x:c r="C514" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D514" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E514" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515">
+      <x:c r="A515" t="n">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B515" t="n">
+        <x:v>2410</x:v>
+      </x:c>
+      <x:c r="C515" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D515" t="str">
+        <x:v>lantern</x:v>
+      </x:c>
+      <x:c r="E515" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516">
+      <x:c r="A516" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B516" t="n">
+        <x:v>2411</x:v>
+      </x:c>
+      <x:c r="C516" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D516" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E516" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517">
+      <x:c r="A517" t="n">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="B517" t="n">
+        <x:v>2411</x:v>
+      </x:c>
+      <x:c r="C517" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D517" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E517" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518">
+      <x:c r="A518" t="n">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B518" t="n">
+        <x:v>2412</x:v>
+      </x:c>
+      <x:c r="C518" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D518" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E518" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519">
+      <x:c r="A519" t="n">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B519" t="n">
+        <x:v>2412</x:v>
+      </x:c>
+      <x:c r="C519" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D519" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E519" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520">
+      <x:c r="A520" t="n">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="B520" t="n">
+        <x:v>2412</x:v>
+      </x:c>
+      <x:c r="C520" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D520" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E520" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521">
+      <x:c r="A521" t="n">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B521" t="n">
+        <x:v>2413</x:v>
+      </x:c>
+      <x:c r="C521" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D521" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E521" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522">
+      <x:c r="A522" t="n">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B522" t="n">
+        <x:v>2413</x:v>
+      </x:c>
+      <x:c r="C522" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D522" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E522" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523">
+      <x:c r="A523" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B523" t="n">
+        <x:v>2413</x:v>
+      </x:c>
+      <x:c r="C523" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D523" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E523" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524">
+      <x:c r="A524" t="n">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B524" t="n">
+        <x:v>2414</x:v>
+      </x:c>
+      <x:c r="C524" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D524" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E524" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525">
+      <x:c r="A525" t="n">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="B525" t="n">
+        <x:v>2414</x:v>
+      </x:c>
+      <x:c r="C525" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D525" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E525" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526">
+      <x:c r="A526" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B526" t="n">
+        <x:v>2415</x:v>
+      </x:c>
+      <x:c r="C526" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D526" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E526" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527">
+      <x:c r="A527" t="n">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B527" t="n">
+        <x:v>2415</x:v>
+      </x:c>
+      <x:c r="C527" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D527" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E527" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528">
+      <x:c r="A528" t="n">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B528" t="n">
+        <x:v>2415</x:v>
+      </x:c>
+      <x:c r="C528" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D528" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E528" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529">
+      <x:c r="A529" t="n">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B529" t="n">
+        <x:v>2415</x:v>
+      </x:c>
+      <x:c r="C529" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D529" t="str">
+        <x:v>clock</x:v>
+      </x:c>
+      <x:c r="E529" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530">
+      <x:c r="A530" t="n">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B530" t="n">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="C530" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D530" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E530" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531">
+      <x:c r="A531" t="n">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B531" t="n">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="C531" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D531" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E531" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532">
+      <x:c r="A532" t="n">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B532" t="n">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="C532" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D532" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E532" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533">
+      <x:c r="A533" t="n">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B533" t="n">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="C533" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D533" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E533" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534">
+      <x:c r="A534" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B534" t="n">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="C534" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D534" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E534" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535">
+      <x:c r="A535" t="n">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B535" t="n">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="C535" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D535" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E535" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536">
+      <x:c r="A536" t="n">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B536" t="n">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="C536" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D536" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E536" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537">
+      <x:c r="A537" t="n">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B537" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="C537" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D537" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E537" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538">
+      <x:c r="A538" t="n">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B538" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="C538" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D538" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E538" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539">
+      <x:c r="A539" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B539" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="C539" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D539" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E539" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540">
+      <x:c r="A540" t="n">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B540" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="C540" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D540" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E540" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541">
+      <x:c r="A541" t="n">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B541" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="C541" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D541" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E541" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542">
+      <x:c r="A542" t="n">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B542" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="C542" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D542" t="str">
+        <x:v>postmaster</x:v>
+      </x:c>
+      <x:c r="E542" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543">
+      <x:c r="A543" t="n">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B543" t="n">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="C543" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D543" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E543" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544">
+      <x:c r="A544" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B544" t="n">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="C544" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D544" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E544" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545">
+      <x:c r="A545" t="n">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B545" t="n">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="C545" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D545" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E545" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546">
+      <x:c r="A546" t="n">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B546" t="n">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="C546" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D546" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E546" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547">
+      <x:c r="A547" t="n">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B547" t="n">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="C547" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D547" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E547" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548">
+      <x:c r="A548" t="n">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B548" t="n">
+        <x:v>2508</x:v>
+      </x:c>
+      <x:c r="C548" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D548" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E548" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549">
+      <x:c r="A549" t="n">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="B549" t="n">
+        <x:v>2508</x:v>
+      </x:c>
+      <x:c r="C549" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D549" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E549" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550">
+      <x:c r="A550" t="n">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B550" t="n">
+        <x:v>2508</x:v>
+      </x:c>
+      <x:c r="C550" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D550" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E550" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551">
+      <x:c r="A551" t="n">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B551" t="n">
+        <x:v>2509</x:v>
+      </x:c>
+      <x:c r="C551" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D551" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E551" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552">
+      <x:c r="A552" t="n">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B552" t="n">
+        <x:v>2509</x:v>
+      </x:c>
+      <x:c r="C552" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D552" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E552" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553">
+      <x:c r="A553" t="n">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B553" t="n">
+        <x:v>2509</x:v>
+      </x:c>
+      <x:c r="C553" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D553" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E553" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554">
+      <x:c r="A554" t="n">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B554" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="C554" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D554" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E554" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555">
+      <x:c r="A555" t="n">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B555" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="C555" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D555" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E555" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556">
+      <x:c r="A556" t="n">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B556" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="C556" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D556" t="str">
+        <x:v>lantern</x:v>
+      </x:c>
+      <x:c r="E556" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557">
+      <x:c r="A557" t="n">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B557" t="n">
+        <x:v>2511</x:v>
+      </x:c>
+      <x:c r="C557" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D557" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E557" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558">
+      <x:c r="A558" t="n">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B558" t="n">
+        <x:v>2511</x:v>
+      </x:c>
+      <x:c r="C558" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D558" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E558" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559">
+      <x:c r="A559" t="n">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B559" t="n">
+        <x:v>2511</x:v>
+      </x:c>
+      <x:c r="C559" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D559" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E559" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560">
+      <x:c r="A560" t="n">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B560" t="n">
+        <x:v>2512</x:v>
+      </x:c>
+      <x:c r="C560" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D560" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E560" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561">
+      <x:c r="A561" t="n">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B561" t="n">
+        <x:v>2512</x:v>
+      </x:c>
+      <x:c r="C561" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D561" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E561" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562">
+      <x:c r="A562" t="n">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B562" t="n">
+        <x:v>2512</x:v>
+      </x:c>
+      <x:c r="C562" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D562" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E562" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563">
+      <x:c r="A563" t="n">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B563" t="n">
+        <x:v>2513</x:v>
+      </x:c>
+      <x:c r="C563" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D563" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E563" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564">
+      <x:c r="A564" t="n">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B564" t="n">
+        <x:v>2513</x:v>
+      </x:c>
+      <x:c r="C564" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D564" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E564" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565">
+      <x:c r="A565" t="n">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B565" t="n">
+        <x:v>2513</x:v>
+      </x:c>
+      <x:c r="C565" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D565" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E565" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566">
+      <x:c r="A566" t="n">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="B566" t="n">
+        <x:v>2514</x:v>
+      </x:c>
+      <x:c r="C566" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D566" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E566" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567">
+      <x:c r="A567" t="n">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B567" t="n">
+        <x:v>2514</x:v>
+      </x:c>
+      <x:c r="C567" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D567" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E567" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568">
+      <x:c r="A568" t="n">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B568" t="n">
+        <x:v>2514</x:v>
+      </x:c>
+      <x:c r="C568" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D568" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E568" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569">
+      <x:c r="A569" t="n">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="B569" t="n">
+        <x:v>2515</x:v>
+      </x:c>
+      <x:c r="C569" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D569" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E569" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570">
+      <x:c r="A570" t="n">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B570" t="n">
+        <x:v>2515</x:v>
+      </x:c>
+      <x:c r="C570" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D570" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E570" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571">
+      <x:c r="A571" t="n">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B571" t="n">
+        <x:v>2515</x:v>
+      </x:c>
+      <x:c r="C571" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D571" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E571" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572">
+      <x:c r="A572" t="n">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B572" t="n">
+        <x:v>2515</x:v>
+      </x:c>
+      <x:c r="C572" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D572" t="str">
+        <x:v>clock</x:v>
+      </x:c>
+      <x:c r="E572" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573">
+      <x:c r="A573" t="n">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B573" t="n">
+        <x:v>2601</x:v>
+      </x:c>
+      <x:c r="C573" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D573" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E573" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574">
+      <x:c r="A574" t="n">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B574" t="n">
+        <x:v>2601</x:v>
+      </x:c>
+      <x:c r="C574" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D574" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E574" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575">
+      <x:c r="A575" t="n">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B575" t="n">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="C575" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D575" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E575" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576">
+      <x:c r="A576" t="n">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B576" t="n">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="C576" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D576" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E576" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577">
+      <x:c r="A577" t="n">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B577" t="n">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="C577" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D577" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E577" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578">
+      <x:c r="A578" t="n">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B578" t="n">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="C578" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D578" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E578" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579">
+      <x:c r="A579" t="n">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B579" t="n">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="C579" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D579" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E579" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580">
+      <x:c r="A580" t="n">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B580" t="n">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="C580" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D580" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E580" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581">
+      <x:c r="A581" t="n">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B581" t="n">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="C581" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D581" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E581" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582">
+      <x:c r="A582" t="n">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B582" t="n">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="C582" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D582" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E582" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583">
+      <x:c r="A583" t="n">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B583" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="C583" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D583" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="E583" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584">
+      <x:c r="A584" t="n">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B584" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="C584" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D584" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E584" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585">
+      <x:c r="A585" t="n">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B585" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="C585" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D585" t="str">
+        <x:v>chef</x:v>
+      </x:c>
+      <x:c r="E585" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586">
+      <x:c r="A586" t="n">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B586" t="n">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="C586" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D586" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E586" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587">
+      <x:c r="A587" t="n">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B587" t="n">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="C587" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D587" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E587" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588">
+      <x:c r="A588" t="n">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B588" t="n">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="C588" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D588" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E588" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589">
+      <x:c r="A589" t="n">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B589" t="n">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="C589" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D589" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E589" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590">
+      <x:c r="A590" t="n">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B590" t="n">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="C590" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D590" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E590" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591">
+      <x:c r="A591" t="n">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B591" t="n">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="C591" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D591" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E591" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592">
+      <x:c r="A592" t="n">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B592" t="n">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="C592" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D592" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E592" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593">
+      <x:c r="A593" t="n">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B593" t="n">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="C593" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D593" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E593" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594">
+      <x:c r="A594" t="n">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B594" t="n">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="C594" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D594" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E594" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595">
+      <x:c r="A595" t="n">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B595" t="n">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="C595" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D595" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E595" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596">
+      <x:c r="A596" t="n">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B596" t="n">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="C596" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D596" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E596" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597">
+      <x:c r="A597" t="n">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B597" t="n">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="C597" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D597" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E597" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598">
+      <x:c r="A598" t="n">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B598" t="n">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="C598" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D598" t="str">
+        <x:v>lantern</x:v>
+      </x:c>
+      <x:c r="E598" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599">
+      <x:c r="A599" t="n">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B599" t="n">
+        <x:v>2611</x:v>
+      </x:c>
+      <x:c r="C599" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D599" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E599" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600">
+      <x:c r="A600" t="n">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B600" t="n">
+        <x:v>2611</x:v>
+      </x:c>
+      <x:c r="C600" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D600" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E600" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601">
+      <x:c r="A601" t="n">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B601" t="n">
+        <x:v>2611</x:v>
+      </x:c>
+      <x:c r="C601" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D601" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E601" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602">
+      <x:c r="A602" t="n">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B602" t="n">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="C602" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D602" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E602" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603">
+      <x:c r="A603" t="n">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B603" t="n">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="C603" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D603" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E603" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604">
+      <x:c r="A604" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B604" t="n">
+        <x:v>2613</x:v>
+      </x:c>
+      <x:c r="C604" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D604" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E604" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605">
+      <x:c r="A605" t="n">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B605" t="n">
+        <x:v>2613</x:v>
+      </x:c>
+      <x:c r="C605" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D605" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E605" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606">
+      <x:c r="A606" t="n">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B606" t="n">
+        <x:v>2613</x:v>
+      </x:c>
+      <x:c r="C606" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D606" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E606" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607">
+      <x:c r="A607" t="n">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B607" t="n">
+        <x:v>2614</x:v>
+      </x:c>
+      <x:c r="C607" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D607" t="str">
+        <x:v>jelly</x:v>
+      </x:c>
+      <x:c r="E607" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608">
+      <x:c r="A608" t="n">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B608" t="n">
+        <x:v>2614</x:v>
+      </x:c>
+      <x:c r="C608" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D608" t="str">
+        <x:v>swift</x:v>
+      </x:c>
+      <x:c r="E608" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609">
+      <x:c r="A609" t="n">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B609" t="n">
+        <x:v>2614</x:v>
+      </x:c>
+      <x:c r="C609" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D609" t="str">
+        <x:v>tank</x:v>
+      </x:c>
+      <x:c r="E609" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610">
+      <x:c r="A610" t="n">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B610" t="n">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="C610" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D610" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E610" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611">
+      <x:c r="A611" t="n">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B611" t="n">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="C611" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D611" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E611" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612">
+      <x:c r="A612" t="n">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B612" t="n">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="C612" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D612" t="str">
+        <x:v>clock</x:v>
+      </x:c>
+      <x:c r="E612" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/WaveGroup.xlsx
+++ b/design/tables/WaveGroup.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="R05a15f7379874a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveGroup" sheetId="1" r:id="R86a7272bdf6d49c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6425,7 +6425,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E359" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="360" ht="48" customHeight="1">
@@ -6442,7 +6442,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E360" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="361" ht="48" customHeight="1">
@@ -6459,7 +6459,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E361" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="362" ht="48" customHeight="1">
@@ -6476,7 +6476,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E362" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="363" ht="48" customHeight="1">
@@ -6493,7 +6493,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E363" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="364" ht="48" customHeight="1">
@@ -6510,7 +6510,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E364" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="365" ht="48" customHeight="1">
@@ -6527,7 +6527,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E365" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="366" ht="48" customHeight="1">
@@ -6544,7 +6544,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E366" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="367" ht="48" customHeight="1">
@@ -6561,7 +6561,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E367" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="368" ht="48" customHeight="1">
@@ -6578,7 +6578,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E368" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="369" ht="48" customHeight="1">
@@ -6595,7 +6595,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E369" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="370" ht="48" customHeight="1">
@@ -6609,10 +6609,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D370" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>postmaster</x:v>
       </x:c>
       <x:c r="E370" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="48" customHeight="1">
@@ -6626,10 +6626,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D371" s="16" t="str">
-        <x:v>postmaster</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E371" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="372" ht="48" customHeight="1">
@@ -6646,7 +6646,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E372" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="373" ht="48" customHeight="1">
@@ -6663,7 +6663,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E373" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="374" ht="48" customHeight="1">
@@ -6680,7 +6680,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E374" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="375" ht="48" customHeight="1">
@@ -6697,7 +6697,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E375" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="376" ht="48" customHeight="1">
@@ -6714,7 +6714,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E376" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="377" ht="48" customHeight="1">
@@ -6731,7 +6731,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E377" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="378" ht="48" customHeight="1">
@@ -6748,7 +6748,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E378" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="379" ht="48" customHeight="1">
@@ -6765,7 +6765,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E379" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="380" ht="48" customHeight="1">
@@ -6782,7 +6782,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E380" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="381" ht="48" customHeight="1">
@@ -6799,7 +6799,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E381" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="382" ht="48" customHeight="1">
@@ -6816,7 +6816,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E382" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="383" ht="48" customHeight="1">
@@ -6833,7 +6833,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E383" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="384" ht="48" customHeight="1">
@@ -6850,7 +6850,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E384" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="385" ht="48" customHeight="1">
@@ -6884,7 +6884,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E386" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="387" ht="48" customHeight="1">
@@ -6901,7 +6901,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E387" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="388" ht="48" customHeight="1">
@@ -6918,7 +6918,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E388" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="389" ht="48" customHeight="1">
@@ -6935,7 +6935,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E389" s="16" t="n">
-        <x:v>12</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="390" ht="48" customHeight="1">
@@ -6952,7 +6952,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E390" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="391" ht="48" customHeight="1">
@@ -6969,7 +6969,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E391" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="392" ht="48" customHeight="1">
@@ -6986,7 +6986,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E392" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="393" ht="48" customHeight="1">
@@ -7003,7 +7003,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E393" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="394" ht="48" customHeight="1">
@@ -7020,7 +7020,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E394" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="395" ht="48" customHeight="1">
@@ -7037,7 +7037,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E395" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="396" ht="48" customHeight="1">
@@ -7054,7 +7054,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E396" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="397" ht="48" customHeight="1">
@@ -7071,7 +7071,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E397" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="398" ht="48" customHeight="1">
@@ -7088,7 +7088,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E398" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="399" ht="48" customHeight="1">
@@ -7105,7 +7105,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E399" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="400" ht="48" customHeight="1">
@@ -7119,10 +7119,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D400" s="16" t="str">
-        <x:v>runner</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E400" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="401" ht="48" customHeight="1">
@@ -7136,10 +7136,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D401" s="16" t="str">
-        <x:v>clock</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E401" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="402" ht="48" customHeight="1">
@@ -7156,7 +7156,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E402" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="403" ht="48" customHeight="1">
@@ -7173,7 +7173,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E403" s="16" t="n">
-        <x:v>7</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="404" ht="48" customHeight="1">
@@ -7190,7 +7190,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E404" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="405" ht="48" customHeight="1">
@@ -7207,7 +7207,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E405" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="406" ht="48" customHeight="1">
@@ -7224,7 +7224,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E406" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="407" ht="48" customHeight="1">
@@ -7241,7 +7241,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E407" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="408" ht="48" customHeight="1">
@@ -7258,7 +7258,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E408" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="409" ht="48" customHeight="1">
@@ -7275,7 +7275,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E409" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="410" ht="48" customHeight="1">
@@ -7292,7 +7292,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E410" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="411" ht="48" customHeight="1">
@@ -7309,7 +7309,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E411" s="16" t="n">
-        <x:v>10</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="412" ht="48" customHeight="1">
@@ -7326,7 +7326,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E412" s="16" t="n">
-        <x:v>3</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="413" ht="48" customHeight="1">
@@ -7343,7 +7343,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E413" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="414" ht="48" customHeight="1">
@@ -7360,7 +7360,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E414" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="415" ht="48" customHeight="1">
@@ -7374,10 +7374,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D415" s="16" t="str">
-        <x:v>shield</x:v>
+        <x:v>postmaster</x:v>
       </x:c>
       <x:c r="E415" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="416" ht="48" customHeight="1">
@@ -7391,10 +7391,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D416" s="16" t="str">
-        <x:v>postmaster</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E416" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="417" ht="48" customHeight="1">
@@ -7411,7 +7411,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E417" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="418" ht="48" customHeight="1">
@@ -7428,7 +7428,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E418" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="419" ht="48" customHeight="1">
@@ -7445,7 +7445,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E419" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="420" ht="48" customHeight="1">
@@ -7462,7 +7462,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E420" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="421" ht="48" customHeight="1">
@@ -7479,7 +7479,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E421" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="422" ht="48" customHeight="1">
@@ -7496,7 +7496,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E422" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="423" ht="48" customHeight="1">
@@ -7513,7 +7513,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E423" s="16" t="n">
-        <x:v>5</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="424" ht="48" customHeight="1">
@@ -7530,7 +7530,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E424" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -7547,7 +7547,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E425" t="n">
-        <x:v>2</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="426">
@@ -7564,7 +7564,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E426" t="n">
-        <x:v>9</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -7581,7 +7581,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E427" t="n">
-        <x:v>6</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -7598,7 +7598,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E428" t="n">
-        <x:v>3</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="429">
@@ -7615,7 +7615,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E429" t="n">
-        <x:v>8</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="430">
@@ -7632,7 +7632,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E430" t="n">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="431">
@@ -7666,7 +7666,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E432" t="n">
-        <x:v>8</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="433">
@@ -7683,7 +7683,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E433" t="n">
-        <x:v>6</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -7700,7 +7700,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E434" t="n">
-        <x:v>3</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -7717,7 +7717,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E435" t="n">
-        <x:v>6</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -7734,7 +7734,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E436" t="n">
-        <x:v>6</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="437">
@@ -7751,7 +7751,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E437" t="n">
-        <x:v>8</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="438">
@@ -7768,7 +7768,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E438" t="n">
-        <x:v>6</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="439">
@@ -7785,7 +7785,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E439" t="n">
-        <x:v>6</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="440">
@@ -7802,7 +7802,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E440" t="n">
-        <x:v>8</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="441">
@@ -7819,7 +7819,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E441" t="n">
-        <x:v>4</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="442">
@@ -7836,7 +7836,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E442" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="443">
@@ -7853,7 +7853,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E443" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="444">
@@ -7870,7 +7870,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E444" t="n">
-        <x:v>4</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="445">
@@ -7887,7 +7887,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E445" t="n">
-        <x:v>5</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="446">
@@ -7904,7 +7904,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E446" t="n">
-        <x:v>11</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="447">
@@ -7918,10 +7918,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D447" t="str">
-        <x:v>shield</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E447" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="448">
@@ -7935,10 +7935,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D448" t="str">
-        <x:v>clock</x:v>
+        <x:v>runner</x:v>
       </x:c>
       <x:c r="E448" t="n">
-        <x:v>1</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -7955,7 +7955,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E449" t="n">
-        <x:v>10</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
@@ -7972,7 +7972,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E450" t="n">
-        <x:v>2</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -7989,7 +7989,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E451" t="n">
-        <x:v>8</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="452">
@@ -8006,7 +8006,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E452" t="n">
-        <x:v>3</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
@@ -8023,7 +8023,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E453" t="n">
-        <x:v>8</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="454">
@@ -8040,7 +8040,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E454" t="n">
-        <x:v>4</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
@@ -8057,7 +8057,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E455" t="n">
-        <x:v>2</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
@@ -8074,7 +8074,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E456" t="n">
-        <x:v>10</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -8091,7 +8091,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E457" t="n">
-        <x:v>5</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
@@ -8108,7 +8108,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E458" t="n">
-        <x:v>3</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="459">
@@ -8125,7 +8125,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E459" t="n">
-        <x:v>8</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
@@ -8139,10 +8139,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D460" t="str">
-        <x:v>shield</x:v>
+        <x:v>chef</x:v>
       </x:c>
       <x:c r="E460" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="461">
@@ -8156,10 +8156,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D461" t="str">
-        <x:v>chef</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E461" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="462">
@@ -8176,7 +8176,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E462" t="n">
-        <x:v>12</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -8193,7 +8193,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E463" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
@@ -8210,7 +8210,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E464" t="n">
-        <x:v>8</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
@@ -8227,7 +8227,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E465" t="n">
-        <x:v>6</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
@@ -8244,7 +8244,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E466" t="n">
-        <x:v>16</x:v>
+        <x:v>511</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -8261,7 +8261,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E467" t="n">
-        <x:v>2</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="468">
@@ -8278,7 +8278,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E468" t="n">
-        <x:v>6</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -8295,7 +8295,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E469" t="n">
-        <x:v>6</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
@@ -8312,7 +8312,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E470" t="n">
-        <x:v>6</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -8329,7 +8329,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E471" t="n">
-        <x:v>8</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
@@ -8346,7 +8346,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E472" t="n">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -8380,7 +8380,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E474" t="n">
-        <x:v>8</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
@@ -8397,7 +8397,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E475" t="n">
-        <x:v>6</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="476">
@@ -8414,7 +8414,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E476" t="n">
-        <x:v>3</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
@@ -8431,7 +8431,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E477" t="n">
-        <x:v>12</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="478">
@@ -8448,7 +8448,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E478" t="n">
-        <x:v>8</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -8465,7 +8465,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E479" t="n">
-        <x:v>6</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
@@ -8482,7 +8482,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E480" t="n">
-        <x:v>6</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -8499,7 +8499,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E481" t="n">
-        <x:v>8</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
@@ -8516,7 +8516,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E482" t="n">
-        <x:v>4</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
@@ -8533,7 +8533,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E483" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="484">
@@ -8550,7 +8550,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E484" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -8567,7 +8567,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E485" t="n">
-        <x:v>4</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
@@ -8584,7 +8584,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E486" t="n">
-        <x:v>10</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -8601,7 +8601,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E487" t="n">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
@@ -8615,10 +8615,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D488" t="str">
-        <x:v>runner</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E488" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
@@ -8632,10 +8632,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D489" t="str">
-        <x:v>clock</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E489" t="n">
-        <x:v>1</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
@@ -8652,7 +8652,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E490" t="n">
-        <x:v>12</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
@@ -8669,7 +8669,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E491" t="n">
-        <x:v>3</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
@@ -8686,7 +8686,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E492" t="n">
-        <x:v>10</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -8703,7 +8703,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E493" t="n">
-        <x:v>3</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="494">
@@ -8720,7 +8720,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E494" t="n">
-        <x:v>10</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -8737,7 +8737,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E495" t="n">
-        <x:v>5</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="496">
@@ -8754,7 +8754,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E496" t="n">
-        <x:v>3</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
@@ -8771,7 +8771,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E497" t="n">
-        <x:v>12</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
@@ -8788,7 +8788,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E498" t="n">
-        <x:v>6</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -8805,7 +8805,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E499" t="n">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
@@ -8822,7 +8822,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E500" t="n">
-        <x:v>10</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
@@ -8836,10 +8836,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D501" t="str">
-        <x:v>shield</x:v>
+        <x:v>chef</x:v>
       </x:c>
       <x:c r="E501" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
@@ -8853,10 +8853,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D502" t="str">
-        <x:v>chef</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E502" t="n">
-        <x:v>1</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -8873,7 +8873,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E503" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
@@ -8890,7 +8890,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E504" t="n">
-        <x:v>4</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
@@ -8907,7 +8907,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E505" t="n">
-        <x:v>5</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="506">
@@ -8924,7 +8924,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E506" t="n">
-        <x:v>10</x:v>
+        <x:v>348</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -8941,7 +8941,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E507" t="n">
-        <x:v>6</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="508">
@@ -8958,7 +8958,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E508" t="n">
-        <x:v>12</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
@@ -8975,7 +8975,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E509" t="n">
-        <x:v>9</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="510">
@@ -8992,7 +8992,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E510" t="n">
-        <x:v>6</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -9009,7 +9009,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E511" t="n">
-        <x:v>6</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="512">
@@ -9026,7 +9026,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E512" t="n">
-        <x:v>7</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
@@ -9043,7 +9043,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E513" t="n">
-        <x:v>10</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -9057,10 +9057,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D514" t="str">
-        <x:v>shield</x:v>
+        <x:v>lantern</x:v>
       </x:c>
       <x:c r="E514" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -9074,10 +9074,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D515" t="str">
-        <x:v>lantern</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E515" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="516">
@@ -9094,7 +9094,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E516" t="n">
-        <x:v>13</x:v>
+        <x:v>430</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
@@ -9111,7 +9111,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E517" t="n">
-        <x:v>6</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="518">
@@ -9128,7 +9128,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E518" t="n">
-        <x:v>14</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -9145,7 +9145,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E519" t="n">
-        <x:v>10</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
@@ -9162,7 +9162,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E520" t="n">
-        <x:v>6</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -9179,7 +9179,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E521" t="n">
-        <x:v>6</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="522">
@@ -9196,7 +9196,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E522" t="n">
-        <x:v>8</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -9213,7 +9213,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E523" t="n">
-        <x:v>4</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="524">
@@ -9230,7 +9230,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E524" t="n">
-        <x:v>16</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -9247,7 +9247,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E525" t="n">
-        <x:v>12</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="526">
@@ -9264,7 +9264,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E526" t="n">
-        <x:v>12</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -9281,7 +9281,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E527" t="n">
-        <x:v>8</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="528">
@@ -9295,10 +9295,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D528" t="str">
-        <x:v>runner</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E528" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
@@ -9312,10 +9312,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D529" t="str">
-        <x:v>clock</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E529" t="n">
-        <x:v>1</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="530">
@@ -9332,7 +9332,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E530" t="n">
-        <x:v>11</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="531">
@@ -9349,7 +9349,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E531" t="n">
-        <x:v>3</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -9366,7 +9366,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E532" t="n">
-        <x:v>9</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="533">
@@ -9383,7 +9383,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E533" t="n">
-        <x:v>3</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="534">
@@ -9400,7 +9400,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E534" t="n">
-        <x:v>9</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
@@ -9417,7 +9417,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E535" t="n">
-        <x:v>5</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="536">
@@ -9434,7 +9434,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E536" t="n">
-        <x:v>2</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="537">
@@ -9451,7 +9451,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E537" t="n">
-        <x:v>11</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="538">
@@ -9468,7 +9468,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E538" t="n">
-        <x:v>6</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="539">
@@ -9485,7 +9485,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E539" t="n">
-        <x:v>3</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="540">
@@ -9502,7 +9502,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E540" t="n">
-        <x:v>9</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="541">
@@ -9516,10 +9516,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D541" t="str">
-        <x:v>shield</x:v>
+        <x:v>postmaster</x:v>
       </x:c>
       <x:c r="E541" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="542">
@@ -9533,10 +9533,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D542" t="str">
-        <x:v>postmaster</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E542" t="n">
-        <x:v>1</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="543">
@@ -9553,7 +9553,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E543" t="n">
-        <x:v>9</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="544">
@@ -9570,7 +9570,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E544" t="n">
-        <x:v>5</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="545">
@@ -9587,7 +9587,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E545" t="n">
-        <x:v>4</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="546">
@@ -9604,7 +9604,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E546" t="n">
-        <x:v>9</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="547">
@@ -9621,7 +9621,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E547" t="n">
-        <x:v>6</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="548">
@@ -9638,7 +9638,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E548" t="n">
-        <x:v>11</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="549">
@@ -9655,7 +9655,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E549" t="n">
-        <x:v>6</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="550">
@@ -9672,7 +9672,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E550" t="n">
-        <x:v>2</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="551">
@@ -9689,7 +9689,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E551" t="n">
-        <x:v>7</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="552">
@@ -9706,7 +9706,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E552" t="n">
-        <x:v>6</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="553">
@@ -9723,7 +9723,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E553" t="n">
-        <x:v>7</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="554">
@@ -9740,7 +9740,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E554" t="n">
-        <x:v>9</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="555">
@@ -9754,10 +9754,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D555" t="str">
-        <x:v>shield</x:v>
+        <x:v>lantern</x:v>
       </x:c>
       <x:c r="E555" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="556">
@@ -9771,7 +9771,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D556" t="str">
-        <x:v>lantern</x:v>
+        <x:v>swift</x:v>
       </x:c>
       <x:c r="E556" t="n">
         <x:v>1</x:v>
@@ -9791,7 +9791,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E557" t="n">
-        <x:v>8</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="558">
@@ -9808,7 +9808,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E558" t="n">
-        <x:v>7</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="559">
@@ -9825,7 +9825,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E559" t="n">
-        <x:v>3</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="560">
@@ -9842,7 +9842,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E560" t="n">
-        <x:v>13</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="561">
@@ -9859,7 +9859,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E561" t="n">
-        <x:v>9</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="562">
@@ -9876,7 +9876,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E562" t="n">
-        <x:v>6</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="563">
@@ -9893,7 +9893,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E563" t="n">
-        <x:v>6</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="564">
@@ -9910,7 +9910,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E564" t="n">
-        <x:v>9</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="565">
@@ -9927,7 +9927,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E565" t="n">
-        <x:v>4</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="566">
@@ -9944,7 +9944,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E566" t="n">
-        <x:v>10</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="567">
@@ -9961,7 +9961,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E567" t="n">
-        <x:v>11</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="568">
@@ -9978,7 +9978,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E568" t="n">
-        <x:v>4</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="569">
@@ -9995,7 +9995,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E569" t="n">
-        <x:v>11</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="570">
@@ -10012,7 +10012,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E570" t="n">
-        <x:v>8</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="571">
@@ -10026,10 +10026,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D571" t="str">
-        <x:v>runner</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E571" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="572">
@@ -10043,10 +10043,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D572" t="str">
-        <x:v>clock</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E572" t="n">
-        <x:v>1</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="573">
@@ -10063,7 +10063,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E573" t="n">
-        <x:v>10</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="574">
@@ -10080,7 +10080,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E574" t="n">
-        <x:v>2</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="575">
@@ -10097,7 +10097,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E575" t="n">
-        <x:v>8</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="576">
@@ -10114,7 +10114,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E576" t="n">
-        <x:v>3</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="577">
@@ -10131,7 +10131,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E577" t="n">
-        <x:v>8</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="578">
@@ -10148,7 +10148,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E578" t="n">
-        <x:v>4</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="579">
@@ -10165,7 +10165,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E579" t="n">
-        <x:v>2</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="580">
@@ -10182,7 +10182,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E580" t="n">
-        <x:v>10</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="581">
@@ -10199,7 +10199,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E581" t="n">
-        <x:v>5</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="582">
@@ -10216,7 +10216,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E582" t="n">
-        <x:v>3</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="583">
@@ -10233,7 +10233,7 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="E583" t="n">
-        <x:v>8</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="584">
@@ -10247,10 +10247,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D584" t="str">
-        <x:v>shield</x:v>
+        <x:v>chef</x:v>
       </x:c>
       <x:c r="E584" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="585">
@@ -10264,10 +10264,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D585" t="str">
-        <x:v>chef</x:v>
+        <x:v>normal</x:v>
       </x:c>
       <x:c r="E585" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="586">
@@ -10284,7 +10284,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E586" t="n">
-        <x:v>6</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="587">
@@ -10301,7 +10301,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E587" t="n">
-        <x:v>4</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="588">
@@ -10318,7 +10318,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E588" t="n">
-        <x:v>4</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="589">
@@ -10335,7 +10335,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E589" t="n">
-        <x:v>8</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="590">
@@ -10352,7 +10352,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E590" t="n">
-        <x:v>6</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="591">
@@ -10369,7 +10369,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E591" t="n">
-        <x:v>7</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="592">
@@ -10386,7 +10386,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E592" t="n">
-        <x:v>6</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="593">
@@ -10403,7 +10403,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E593" t="n">
-        <x:v>2</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="594">
@@ -10420,7 +10420,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E594" t="n">
-        <x:v>6</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="595">
@@ -10437,7 +10437,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E595" t="n">
-        <x:v>11</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="596">
@@ -10454,7 +10454,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E596" t="n">
-        <x:v>8</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="597">
@@ -10471,7 +10471,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E597" t="n">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="598">
@@ -10505,7 +10505,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E599" t="n">
-        <x:v>8</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="600">
@@ -10522,7 +10522,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E600" t="n">
-        <x:v>6</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="601">
@@ -10539,7 +10539,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E601" t="n">
-        <x:v>3</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="602">
@@ -10556,7 +10556,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E602" t="n">
-        <x:v>15</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="603">
@@ -10573,7 +10573,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E603" t="n">
-        <x:v>8</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="604">
@@ -10590,7 +10590,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E604" t="n">
-        <x:v>6</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="605">
@@ -10607,7 +10607,7 @@
         <x:v>runner</x:v>
       </x:c>
       <x:c r="E605" t="n">
-        <x:v>8</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="606">
@@ -10624,7 +10624,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E606" t="n">
-        <x:v>4</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="607">
@@ -10641,7 +10641,7 @@
         <x:v>jelly</x:v>
       </x:c>
       <x:c r="E607" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="608">
@@ -10658,7 +10658,7 @@
         <x:v>swift</x:v>
       </x:c>
       <x:c r="E608" t="n">
-        <x:v>10</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="609">
@@ -10675,7 +10675,7 @@
         <x:v>tank</x:v>
       </x:c>
       <x:c r="E609" t="n">
-        <x:v>4</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="610">
@@ -10692,7 +10692,7 @@
         <x:v>shield</x:v>
       </x:c>
       <x:c r="E610" t="n">
-        <x:v>15</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="611">
@@ -10706,10 +10706,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D611" t="str">
-        <x:v>runner</x:v>
+        <x:v>clock</x:v>
       </x:c>
       <x:c r="E611" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="612">
@@ -10723,10 +10723,316 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D612" t="str">
-        <x:v>clock</x:v>
+        <x:v>shield</x:v>
       </x:c>
       <x:c r="E612" t="n">
-        <x:v>1</x:v>
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613">
+      <x:c r="A613" t="n">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B613" t="n">
+        <x:v>2105</x:v>
+      </x:c>
+      <x:c r="C613" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D613" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E613" t="n">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614">
+      <x:c r="A614" t="n">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B614" t="n">
+        <x:v>2110</x:v>
+      </x:c>
+      <x:c r="C614" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D614" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E614" t="n">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615">
+      <x:c r="A615" t="n">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B615" t="n">
+        <x:v>2115</x:v>
+      </x:c>
+      <x:c r="C615" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D615" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E615" t="n">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616">
+      <x:c r="A616" t="n">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B616" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="C616" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D616" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E616" t="n">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617">
+      <x:c r="A617" t="n">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B617" t="n">
+        <x:v>2210</x:v>
+      </x:c>
+      <x:c r="C617" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D617" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E617" t="n">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618">
+      <x:c r="A618" t="n">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="B618" t="n">
+        <x:v>2215</x:v>
+      </x:c>
+      <x:c r="C618" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D618" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E618" t="n">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619">
+      <x:c r="A619" t="n">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B619" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="C619" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D619" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E619" t="n">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620">
+      <x:c r="A620" t="n">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="B620" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="C620" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D620" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E620" t="n">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621">
+      <x:c r="A621" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B621" t="n">
+        <x:v>2315</x:v>
+      </x:c>
+      <x:c r="C621" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D621" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E621" t="n">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622">
+      <x:c r="A622" t="n">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B622" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="C622" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D622" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E622" t="n">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623">
+      <x:c r="A623" t="n">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="B623" t="n">
+        <x:v>2410</x:v>
+      </x:c>
+      <x:c r="C623" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D623" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E623" t="n">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624">
+      <x:c r="A624" t="n">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="B624" t="n">
+        <x:v>2415</x:v>
+      </x:c>
+      <x:c r="C624" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D624" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E624" t="n">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625">
+      <x:c r="A625" t="n">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="B625" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="C625" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D625" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E625" t="n">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626">
+      <x:c r="A626" t="n">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="B626" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="C626" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D626" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E626" t="n">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627">
+      <x:c r="A627" t="n">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="B627" t="n">
+        <x:v>2515</x:v>
+      </x:c>
+      <x:c r="C627" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D627" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E627" t="n">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628">
+      <x:c r="A628" t="n">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="B628" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="C628" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D628" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E628" t="n">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629">
+      <x:c r="A629" t="n">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="B629" t="n">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="C629" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D629" t="str">
+        <x:v>shield</x:v>
+      </x:c>
+      <x:c r="E629" t="n">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630">
+      <x:c r="A630" t="n">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="B630" t="n">
+        <x:v>2615</x:v>
+      </x:c>
+      <x:c r="C630" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D630" t="str">
+        <x:v>runner</x:v>
+      </x:c>
+      <x:c r="E630" t="n">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
